--- a/AHR 30th/AHR_data 30th dashboard.xlsx
+++ b/AHR 30th/AHR_data 30th dashboard.xlsx
@@ -405,7 +405,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -438,7 +438,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="151">
       <c r="A151">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
     </row>
     <row r="153">
       <c r="A153">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="188">
       <c r="A188">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="189">
       <c r="A189">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="191">
       <c r="A191">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="193">
       <c r="A193">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="196">
       <c r="A196">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
     </row>
     <row r="197">
       <c r="A197">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="199">
       <c r="A199">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="201">
       <c r="A201">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="203">
       <c r="A203">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="204">
       <c r="A204">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
     </row>
     <row r="205">
       <c r="A205">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
     </row>
     <row r="206">
       <c r="A206">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
     </row>
     <row r="207">
       <c r="A207">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="208">
       <c r="A208">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
     </row>
     <row r="209">
       <c r="A209">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
     </row>
     <row r="215">
       <c r="A215">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="216">
       <c r="A216">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="223">
       <c r="A223">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="227">
       <c r="A227">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="232">
       <c r="A232">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
     </row>
     <row r="233">
       <c r="A233">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="234">
       <c r="A234">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
     </row>
     <row r="239">
       <c r="A239">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="240">
       <c r="A240">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
     </row>
     <row r="241">
       <c r="A241">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
     </row>
     <row r="242">
       <c r="A242">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
     </row>
     <row r="243">
       <c r="A243">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
     </row>
     <row r="245">
       <c r="A245">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
     </row>
     <row r="246">
       <c r="A246">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
     </row>
     <row r="249">
       <c r="A249">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
     </row>
     <row r="250">
       <c r="A250">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
     </row>
     <row r="251">
       <c r="A251">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
     </row>
     <row r="253">
       <c r="A253">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
     </row>
     <row r="254">
       <c r="A254">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
     </row>
     <row r="255">
       <c r="A255">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
     </row>
     <row r="256">
       <c r="A256">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
     </row>
     <row r="257">
       <c r="A257">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
     </row>
     <row r="259">
       <c r="A259">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
     </row>
     <row r="260">
       <c r="A260">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
     </row>
     <row r="261">
       <c r="A261">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="263">
       <c r="A263">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
     </row>
     <row r="265">
       <c r="A265">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="266">
       <c r="A266">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
     </row>
     <row r="267">
       <c r="A267">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
     </row>
     <row r="268">
       <c r="A268">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
     </row>
     <row r="269">
       <c r="A269">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
     </row>
     <row r="274">
       <c r="A274">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
     </row>
     <row r="275">
       <c r="A275">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
     </row>
     <row r="276">
       <c r="A276">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
     </row>
     <row r="277">
       <c r="A277">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
     </row>
     <row r="283">
       <c r="A283">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="284">
       <c r="A284">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
     </row>
     <row r="285">
       <c r="A285">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="286">
       <c r="A286">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
     </row>
     <row r="287">
       <c r="A287">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
     </row>
     <row r="289">
       <c r="A289">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
     </row>
     <row r="290">
       <c r="A290">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
     </row>
     <row r="291">
       <c r="A291">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
     </row>
     <row r="292">
       <c r="A292">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
     </row>
     <row r="293">
       <c r="A293">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="294">
       <c r="A294">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
     </row>
     <row r="295">
       <c r="A295">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
     </row>
     <row r="296">
       <c r="A296">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
     </row>
     <row r="297">
       <c r="A297">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
     </row>
     <row r="298">
       <c r="A298">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
     </row>
     <row r="299">
       <c r="A299">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
     </row>
     <row r="301">
       <c r="A301">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
     </row>
     <row r="302">
       <c r="A302">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="305">
       <c r="A305">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
     </row>
     <row r="309">
       <c r="A309">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
     </row>
     <row r="311">
       <c r="A311">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="314">
       <c r="A314">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
     </row>
     <row r="315">
       <c r="A315">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
     </row>
     <row r="321">
       <c r="A321">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
     </row>
     <row r="329">
       <c r="A329">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
     </row>
     <row r="330">
       <c r="A330">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
     </row>
     <row r="331">
       <c r="A331">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="338">
       <c r="A338">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
     </row>
     <row r="381">
       <c r="A381">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
     </row>
     <row r="383">
       <c r="A383">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="384">
       <c r="A384">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
     </row>
     <row r="385">
       <c r="A385">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
     </row>
     <row r="386">
       <c r="A386">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
     </row>
     <row r="390">
       <c r="A390">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
     </row>
     <row r="392">
       <c r="A392">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
     </row>
     <row r="393">
       <c r="A393">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
     </row>
     <row r="395">
       <c r="A395">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
     </row>
     <row r="396">
       <c r="A396">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
     </row>
     <row r="397">
       <c r="A397">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="398">
       <c r="A398">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
     </row>
     <row r="399">
       <c r="A399">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
     </row>
     <row r="400">
       <c r="A400">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
     </row>
     <row r="401">
       <c r="A401">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
     </row>
     <row r="402">
       <c r="A402">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
     </row>
     <row r="403">
       <c r="A403">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
     </row>
     <row r="404">
       <c r="A404">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
     </row>
     <row r="405">
       <c r="A405">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
     </row>
     <row r="406">
       <c r="A406">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="407">
       <c r="A407">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
     </row>
     <row r="408">
       <c r="A408">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
     </row>
     <row r="409">
       <c r="A409">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
     </row>
     <row r="410">
       <c r="A410">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
     </row>
     <row r="411">
       <c r="A411">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
     </row>
     <row r="412">
       <c r="A412">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
     </row>
     <row r="413">
       <c r="A413">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
     </row>
     <row r="414">
       <c r="A414">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
     </row>
     <row r="415">
       <c r="A415">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
     </row>
     <row r="416">
       <c r="A416">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
     </row>
     <row r="417">
       <c r="A417">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
     </row>
     <row r="418">
       <c r="A418">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
     </row>
     <row r="419">
       <c r="A419">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
     </row>
     <row r="420">
       <c r="A420">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
     </row>
     <row r="421">
       <c r="A421">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
     </row>
     <row r="422">
       <c r="A422">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
     </row>
     <row r="423">
       <c r="A423">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
     </row>
     <row r="424">
       <c r="A424">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
     </row>
     <row r="425">
       <c r="A425">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
     </row>
     <row r="426">
       <c r="A426">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
     </row>
     <row r="427">
       <c r="A427">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
     </row>
     <row r="428">
       <c r="A428">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
     </row>
     <row r="429">
       <c r="A429">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
     </row>
     <row r="430">
       <c r="A430">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
     </row>
     <row r="431">
       <c r="A431">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
     </row>
     <row r="432">
       <c r="A432">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
     </row>
     <row r="433">
       <c r="A433">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
     </row>
     <row r="434">
       <c r="A434">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
     </row>
     <row r="435">
       <c r="A435">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
     </row>
     <row r="436">
       <c r="A436">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
     </row>
     <row r="437">
       <c r="A437">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
     </row>
     <row r="438">
       <c r="A438">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
     </row>
     <row r="439">
       <c r="A439">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
     </row>
     <row r="440">
       <c r="A440">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
     </row>
     <row r="441">
       <c r="A441">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
     </row>
     <row r="442">
       <c r="A442">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
     </row>
     <row r="443">
       <c r="A443">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
     </row>
     <row r="444">
       <c r="A444">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
     </row>
     <row r="445">
       <c r="A445">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
     </row>
     <row r="446">
       <c r="A446">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
     </row>
     <row r="447">
       <c r="A447">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
     </row>
     <row r="448">
       <c r="A448">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
     </row>
     <row r="449">
       <c r="A449">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
     </row>
     <row r="450">
       <c r="A450">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
     </row>
     <row r="451">
       <c r="A451">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
     </row>
     <row r="452">
       <c r="A452">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
     </row>
     <row r="453">
       <c r="A453">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
     </row>
     <row r="454">
       <c r="A454">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
     </row>
     <row r="455">
       <c r="A455">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
     </row>
     <row r="456">
       <c r="A456">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
     </row>
     <row r="457">
       <c r="A457">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
     </row>
     <row r="458">
       <c r="A458">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
     </row>
     <row r="459">
       <c r="A459">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
     </row>
     <row r="460">
       <c r="A460">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
     </row>
     <row r="461">
       <c r="A461">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
     </row>
     <row r="462">
       <c r="A462">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
     </row>
     <row r="463">
       <c r="A463">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
     </row>
     <row r="464">
       <c r="A464">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
     </row>
     <row r="465">
       <c r="A465">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
     </row>
     <row r="466">
       <c r="A466">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
     </row>
     <row r="467">
       <c r="A467">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
     </row>
     <row r="468">
       <c r="A468">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
     </row>
     <row r="469">
       <c r="A469">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
     </row>
     <row r="470">
       <c r="A470">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
     </row>
     <row r="471">
       <c r="A471">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
     </row>
     <row r="472">
       <c r="A472">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
     </row>
     <row r="473">
       <c r="A473">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
     </row>
     <row r="474">
       <c r="A474">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
     </row>
     <row r="475">
       <c r="A475">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
     </row>
     <row r="476">
       <c r="A476">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
     </row>
     <row r="477">
       <c r="A477">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
     </row>
     <row r="478">
       <c r="A478">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
     </row>
     <row r="479">
       <c r="A479">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
     </row>
     <row r="480">
       <c r="A480">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
     </row>
     <row r="481">
       <c r="A481">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
     </row>
     <row r="482">
       <c r="A482">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
     </row>
     <row r="483">
       <c r="A483">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
     </row>
     <row r="484">
       <c r="A484">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
     </row>
     <row r="485">
       <c r="A485">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
     </row>
     <row r="486">
       <c r="A486">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
     </row>
     <row r="487">
       <c r="A487">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
     </row>
     <row r="488">
       <c r="A488">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
     </row>
     <row r="489">
       <c r="A489">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
     </row>
     <row r="490">
       <c r="A490">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
     </row>
     <row r="491">
       <c r="A491">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
     </row>
     <row r="492">
       <c r="A492">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
     </row>
     <row r="493">
       <c r="A493">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
     </row>
     <row r="494">
       <c r="A494">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
     </row>
     <row r="495">
       <c r="A495">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
     </row>
     <row r="496">
       <c r="A496">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
     </row>
     <row r="497">
       <c r="A497">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
     </row>
     <row r="498">
       <c r="A498">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
     </row>
     <row r="499">
       <c r="A499">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
     </row>
     <row r="500">
       <c r="A500">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
     </row>
     <row r="501">
       <c r="A501">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
     </row>
     <row r="502">
       <c r="A502">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -16917,10 +16917,19 @@
       <c r="F502">
         <v>1.546558739611991</v>
       </c>
+      <c r="G502">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H502">
+        <v>1.343662560004414</v>
+      </c>
+      <c r="I502">
+        <v>41</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -16941,10 +16950,19 @@
       <c r="F503">
         <v>1.916588853159228</v>
       </c>
+      <c r="G503">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H503">
+        <v>1.665147672023079</v>
+      </c>
+      <c r="I503">
+        <v>48</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -16965,10 +16983,19 @@
       <c r="F504">
         <v>1.437964708203125</v>
       </c>
+      <c r="G504">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H504">
+        <v>1.249315199954809</v>
+      </c>
+      <c r="I504">
+        <v>39</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -16989,10 +17016,19 @@
       <c r="F505">
         <v>1.791750853497073</v>
       </c>
+      <c r="G505">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H505">
+        <v>1.556687422880544</v>
+      </c>
+      <c r="I505">
+        <v>47</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -17013,10 +17049,19 @@
       <c r="F506">
         <v>1.158444012988471</v>
       </c>
+      <c r="G506">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H506">
+        <v>1.006465391999526</v>
+      </c>
+      <c r="I506">
+        <v>30</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -17037,10 +17082,19 @@
       <c r="F507">
         <v>1.323958484081296</v>
       </c>
+      <c r="G507">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H507">
+        <v>1.150265683737659</v>
+      </c>
+      <c r="I507">
+        <v>35</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -17061,10 +17115,19 @@
       <c r="F508">
         <v>0.557401017424077</v>
       </c>
+      <c r="G508">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H508">
+        <v>0.484274446768833</v>
+      </c>
+      <c r="I508">
+        <v>3</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -17085,10 +17148,19 @@
       <c r="F509">
         <v>0.9435103377597176</v>
       </c>
+      <c r="G509">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H509">
+        <v>0.8197293018064832</v>
+      </c>
+      <c r="I509">
+        <v>18</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -17109,10 +17181,19 @@
       <c r="F510">
         <v>1.54518544526613</v>
       </c>
+      <c r="G510">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H510">
+        <v>1.342469430930725</v>
+      </c>
+      <c r="I510">
+        <v>40</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -17133,10 +17214,19 @@
       <c r="F511">
         <v>0.8306768720704029</v>
       </c>
+      <c r="G511">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H511">
+        <v>0.7216986874631109</v>
+      </c>
+      <c r="I511">
+        <v>13</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -17157,10 +17247,19 @@
       <c r="F512">
         <v>3.143211060938769</v>
       </c>
+      <c r="G512">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H512">
+        <v>2.730846823079459</v>
+      </c>
+      <c r="I512">
+        <v>49</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -17181,10 +17280,19 @@
       <c r="F513">
         <v>1.424057155134427</v>
       </c>
+      <c r="G513">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H513">
+        <v>1.237232206996926</v>
+      </c>
+      <c r="I513">
+        <v>38</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -17205,10 +17313,19 @@
       <c r="F514">
         <v>0.9563043256849029</v>
       </c>
+      <c r="G514">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H514">
+        <v>0.8308448204918795</v>
+      </c>
+      <c r="I514">
+        <v>20</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -17229,10 +17346,19 @@
       <c r="F515">
         <v>1.042099344822047</v>
       </c>
+      <c r="G515">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H515">
+        <v>0.9053842169575864</v>
+      </c>
+      <c r="I515">
+        <v>25</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -17253,10 +17379,19 @@
       <c r="F516">
         <v>0.64135605439773</v>
       </c>
+      <c r="G516">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H516">
+        <v>0.5572152520651036</v>
+      </c>
+      <c r="I516">
+        <v>8</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -17277,10 +17412,19 @@
       <c r="F517">
         <v>0.9315724843391602</v>
       </c>
+      <c r="G517">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H517">
+        <v>0.809357599602629</v>
+      </c>
+      <c r="I517">
+        <v>17</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -17301,10 +17445,19 @@
       <c r="F518">
         <v>1.023625905976862</v>
       </c>
+      <c r="G518">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H518">
+        <v>0.8893343460441584</v>
+      </c>
+      <c r="I518">
+        <v>23</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -17325,10 +17478,19 @@
       <c r="F519">
         <v>0.9691454880831557</v>
       </c>
+      <c r="G519">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H519">
+        <v>0.8420013247354865</v>
+      </c>
+      <c r="I519">
+        <v>22</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -17349,10 +17511,19 @@
       <c r="F520">
         <v>1.077728692938083</v>
       </c>
+      <c r="G520">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H520">
+        <v>0.9363392785887356</v>
+      </c>
+      <c r="I520">
+        <v>28</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -17373,10 +17544,19 @@
       <c r="F521">
         <v>0.5978690522960789</v>
       </c>
+      <c r="G521">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H521">
+        <v>0.5194333980208908</v>
+      </c>
+      <c r="I521">
+        <v>7</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -17397,10 +17577,19 @@
       <c r="F522">
         <v>0.7424728473967344</v>
       </c>
+      <c r="G522">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H522">
+        <v>0.6450663277860074</v>
+      </c>
+      <c r="I522">
+        <v>11</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -17421,10 +17610,19 @@
       <c r="F523">
         <v>0.8125484229061878</v>
       </c>
+      <c r="G523">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H523">
+        <v>0.7059485463342907</v>
+      </c>
+      <c r="I523">
+        <v>12</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -17445,10 +17643,19 @@
       <c r="F524">
         <v>0.8978072570646936</v>
       </c>
+      <c r="G524">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H524">
+        <v>0.7800221010168312</v>
+      </c>
+      <c r="I524">
+        <v>15</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -17469,10 +17676,19 @@
       <c r="F525">
         <v>1.652932463280736</v>
       </c>
+      <c r="G525">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H525">
+        <v>1.436080898992177</v>
+      </c>
+      <c r="I525">
+        <v>43</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -17493,10 +17709,19 @@
       <c r="F526">
         <v>1.038530651512329</v>
       </c>
+      <c r="G526">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H526">
+        <v>0.9022837077654113</v>
+      </c>
+      <c r="I526">
+        <v>24</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -17517,10 +17742,19 @@
       <c r="F527">
         <v>1.265166521633523</v>
       </c>
+      <c r="G527">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H527">
+        <v>1.099186758154736</v>
+      </c>
+      <c r="I527">
+        <v>34</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -17541,10 +17775,19 @@
       <c r="F528">
         <v>1.158331431633449</v>
       </c>
+      <c r="G528">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H528">
+        <v>1.00636758042094</v>
+      </c>
+      <c r="I528">
+        <v>29</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -17565,10 +17808,19 @@
       <c r="F529">
         <v>1.331149152665648</v>
       </c>
+      <c r="G529">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H529">
+        <v>1.156512993917818</v>
+      </c>
+      <c r="I529">
+        <v>36</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -17589,10 +17841,19 @@
       <c r="F530">
         <v>0.8989784599538359</v>
       </c>
+      <c r="G530">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H530">
+        <v>0.7810396514221293</v>
+      </c>
+      <c r="I530">
+        <v>16</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -17613,10 +17874,19 @@
       <c r="F531">
         <v>1.757109056582949</v>
       </c>
+      <c r="G531">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H531">
+        <v>1.526590353605009</v>
+      </c>
+      <c r="I531">
+        <v>46</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -17637,10 +17907,19 @@
       <c r="F532">
         <v>1.621249915389613</v>
       </c>
+      <c r="G532">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H532">
+        <v>1.408554848854871</v>
+      </c>
+      <c r="I532">
+        <v>42</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -17661,10 +17940,19 @@
       <c r="F533">
         <v>0.5653356515936899</v>
       </c>
+      <c r="G533">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H533">
+        <v>0.4911681201793336</v>
+      </c>
+      <c r="I533">
+        <v>4</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -17685,10 +17973,19 @@
       <c r="F534">
         <v>1.176656778823377</v>
       </c>
+      <c r="G534">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H534">
+        <v>1.022288788123899</v>
+      </c>
+      <c r="I534">
+        <v>31</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -17709,10 +18006,19 @@
       <c r="F535">
         <v>0.8899499884751475</v>
       </c>
+      <c r="G535">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H535">
+        <v>0.7731956434389442</v>
+      </c>
+      <c r="I535">
+        <v>14</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -17733,10 +18039,19 @@
       <c r="F536">
         <v>0.6690928544011803</v>
       </c>
+      <c r="G536">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H536">
+        <v>0.5813132049875491</v>
+      </c>
+      <c r="I536">
+        <v>9</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -17757,10 +18072,19 @@
       <c r="F537">
         <v>0.9574745409619284</v>
       </c>
+      <c r="G537">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H537">
+        <v>0.8318615128518986</v>
+      </c>
+      <c r="I537">
+        <v>21</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -17781,10 +18105,19 @@
       <c r="F538">
         <v>1.674049694553563</v>
       </c>
+      <c r="G538">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H538">
+        <v>1.454427717839401</v>
+      </c>
+      <c r="I538">
+        <v>44</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -17805,10 +18138,19 @@
       <c r="F539">
         <v>0.5812995077504219</v>
       </c>
+      <c r="G539">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H539">
+        <v>0.5050376456501077</v>
+      </c>
+      <c r="I539">
+        <v>6</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -17829,10 +18171,19 @@
       <c r="F540">
         <v>0.5727315192711556</v>
       </c>
+      <c r="G540">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H540">
+        <v>0.4975937089671547</v>
+      </c>
+      <c r="I540">
+        <v>5</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -17853,10 +18204,19 @@
       <c r="F541">
         <v>1.732935271076938</v>
       </c>
+      <c r="G541">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H541">
+        <v>1.505587976077368</v>
+      </c>
+      <c r="I541">
+        <v>45</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -17877,10 +18237,19 @@
       <c r="F542">
         <v>1.075570109353639</v>
       </c>
+      <c r="G542">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H542">
+        <v>0.9344638839653246</v>
+      </c>
+      <c r="I542">
+        <v>27</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -17895,10 +18264,13 @@
           <t>rural_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="G543">
+        <v>1.151002331721522</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -17919,10 +18291,19 @@
       <c r="F544">
         <v>1.337922335752768</v>
       </c>
+      <c r="G544">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H544">
+        <v>1.162397589370366</v>
+      </c>
+      <c r="I544">
+        <v>37</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -17943,10 +18324,19 @@
       <c r="F545">
         <v>1.180604144687008</v>
       </c>
+      <c r="G545">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H545">
+        <v>1.025718291049169</v>
+      </c>
+      <c r="I545">
+        <v>32</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -17967,10 +18357,19 @@
       <c r="F546">
         <v>0.5408658706973106</v>
       </c>
+      <c r="G546">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H546">
+        <v>0.4699085794972739</v>
+      </c>
+      <c r="I546">
+        <v>2</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -17991,10 +18390,19 @@
       <c r="F547">
         <v>1.25354972894032</v>
       </c>
+      <c r="G547">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H547">
+        <v>1.089093996069861</v>
+      </c>
+      <c r="I547">
+        <v>33</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -18015,10 +18423,19 @@
       <c r="F548">
         <v>1.053732927431458</v>
       </c>
+      <c r="G548">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H548">
+        <v>0.9154915662554906</v>
+      </c>
+      <c r="I548">
+        <v>26</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -18039,10 +18456,19 @@
       <c r="F549">
         <v>0.711916799512206</v>
       </c>
+      <c r="G549">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H549">
+        <v>0.6185189898333322</v>
+      </c>
+      <c r="I549">
+        <v>10</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -18063,10 +18489,19 @@
       <c r="F550">
         <v>0.4906469365723513</v>
       </c>
+      <c r="G550">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H550">
+        <v>0.4262779692535499</v>
+      </c>
+      <c r="I550">
+        <v>1</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -18087,10 +18522,19 @@
       <c r="F551">
         <v>0.9495847396975362</v>
       </c>
+      <c r="G551">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="H551">
+        <v>0.8250067906267997</v>
+      </c>
+      <c r="I551">
+        <v>19</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -18111,10 +18555,19 @@
       <c r="F552">
         <v>1.061679741146842</v>
       </c>
+      <c r="G552">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H552">
+        <v>1.105390411122654</v>
+      </c>
+      <c r="I552">
+        <v>36</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -18135,10 +18588,19 @@
       <c r="F553">
         <v>1.261411418464348</v>
       </c>
+      <c r="G553">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H553">
+        <v>1.313345288989801</v>
+      </c>
+      <c r="I553">
+        <v>45</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -18159,10 +18621,19 @@
       <c r="F554">
         <v>1.23537942968035</v>
       </c>
+      <c r="G554">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H554">
+        <v>1.286241530983455</v>
+      </c>
+      <c r="I554">
+        <v>43</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -18183,10 +18654,19 @@
       <c r="F555">
         <v>0.9822082835756718</v>
       </c>
+      <c r="G555">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H555">
+        <v>1.022647015207217</v>
+      </c>
+      <c r="I555">
+        <v>26</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -18207,10 +18687,19 @@
       <c r="F556">
         <v>0.9125068253040979</v>
       </c>
+      <c r="G556">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H556">
+        <v>0.9500758615639947</v>
+      </c>
+      <c r="I556">
+        <v>23</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -18231,10 +18720,19 @@
       <c r="F557">
         <v>1.191299959746605</v>
       </c>
+      <c r="G557">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H557">
+        <v>1.240347254674201</v>
+      </c>
+      <c r="I557">
+        <v>41</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -18255,10 +18753,19 @@
       <c r="F558">
         <v>0.7196827190122299</v>
       </c>
+      <c r="G558">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H558">
+        <v>0.7493129479775652</v>
+      </c>
+      <c r="I558">
+        <v>19</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -18279,10 +18786,19 @@
       <c r="F559">
         <v>0.9913191410168661</v>
       </c>
+      <c r="G559">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H559">
+        <v>1.032132977934284</v>
+      </c>
+      <c r="I559">
+        <v>27</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -18303,10 +18819,19 @@
       <c r="F560">
         <v>1.175569279528065</v>
       </c>
+      <c r="G560">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H560">
+        <v>1.223968922866506</v>
+      </c>
+      <c r="I560">
+        <v>39</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -18327,10 +18852,19 @@
       <c r="F561">
         <v>1.031157054593156</v>
       </c>
+      <c r="G561">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H561">
+        <v>1.073611067757111</v>
+      </c>
+      <c r="I561">
+        <v>32</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -18351,10 +18885,19 @@
       <c r="F562">
         <v>1.143791676866334</v>
       </c>
+      <c r="G562">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H562">
+        <v>1.190882996942366</v>
+      </c>
+      <c r="I562">
+        <v>38</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -18375,10 +18918,19 @@
       <c r="F563">
         <v>0.6697451321627513</v>
       </c>
+      <c r="G563">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H563">
+        <v>0.6973193688230925</v>
+      </c>
+      <c r="I563">
+        <v>11</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -18399,10 +18951,19 @@
       <c r="F564">
         <v>0.9713350183635551</v>
       </c>
+      <c r="G564">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H564">
+        <v>1.011326084198319</v>
+      </c>
+      <c r="I564">
+        <v>25</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -18423,10 +18984,19 @@
       <c r="F565">
         <v>0.6881759063033738</v>
       </c>
+      <c r="G565">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H565">
+        <v>0.7165089607640709</v>
+      </c>
+      <c r="I565">
+        <v>16</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -18447,10 +19017,19 @@
       <c r="F566">
         <v>0.6477854046018922</v>
       </c>
+      <c r="G566">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H566">
+        <v>0.6744555320784841</v>
+      </c>
+      <c r="I566">
+        <v>10</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -18471,10 +19050,19 @@
       <c r="F567">
         <v>0.6714571986417301</v>
       </c>
+      <c r="G567">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H567">
+        <v>0.6991019231996349</v>
+      </c>
+      <c r="I567">
+        <v>13</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -18495,10 +19083,19 @@
       <c r="F568">
         <v>0.9664382251635665</v>
       </c>
+      <c r="G568">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H568">
+        <v>1.006227683956952</v>
+      </c>
+      <c r="I568">
+        <v>24</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -18519,10 +19116,19 @@
       <c r="F569">
         <v>1.199541949337344</v>
       </c>
+      <c r="G569">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H569">
+        <v>1.2489285771852</v>
+      </c>
+      <c r="I569">
+        <v>42</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -18543,10 +19149,19 @@
       <c r="F570">
         <v>0.5028678933106425</v>
       </c>
+      <c r="G570">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H570">
+        <v>0.5235715873475935</v>
+      </c>
+      <c r="I570">
+        <v>3</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -18567,10 +19182,19 @@
       <c r="F571">
         <v>1.011113274179578</v>
       </c>
+      <c r="G571">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H571">
+        <v>1.052742060076994</v>
+      </c>
+      <c r="I571">
+        <v>28</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -18591,10 +19215,19 @@
       <c r="F572">
         <v>0.5233313811194925</v>
       </c>
+      <c r="G572">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H572">
+        <v>0.5448775822963089</v>
+      </c>
+      <c r="I572">
+        <v>6</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -18615,10 +19248,19 @@
       <c r="F573">
         <v>0.8461012176731455</v>
       </c>
+      <c r="G573">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H573">
+        <v>0.8809362528146218</v>
+      </c>
+      <c r="I573">
+        <v>21</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -18639,10 +19281,19 @@
       <c r="F574">
         <v>0.3507276065045727</v>
       </c>
+      <c r="G574">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H574">
+        <v>0.3651674964875611</v>
+      </c>
+      <c r="I574">
+        <v>2</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -18663,10 +19314,19 @@
       <c r="F575">
         <v>1.500817967161366</v>
       </c>
+      <c r="G575">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H575">
+        <v>1.562608501833805</v>
+      </c>
+      <c r="I575">
+        <v>49</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -18687,10 +19347,19 @@
       <c r="F576">
         <v>1.023679431315542</v>
       </c>
+      <c r="G576">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H576">
+        <v>1.065825581467118</v>
+      </c>
+      <c r="I576">
+        <v>31</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -18711,10 +19380,19 @@
       <c r="F577">
         <v>1.446432915893151</v>
       </c>
+      <c r="G577">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H577">
+        <v>1.505984350641695</v>
+      </c>
+      <c r="I577">
+        <v>48</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -18735,10 +19413,19 @@
       <c r="F578">
         <v>0.7859966683846932</v>
       </c>
+      <c r="G578">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H578">
+        <v>0.8183571247844159</v>
+      </c>
+      <c r="I578">
+        <v>20</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -18759,10 +19446,19 @@
       <c r="F579">
         <v>1.182648816398851</v>
       </c>
+      <c r="G579">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H579">
+        <v>1.231339933039217</v>
+      </c>
+      <c r="I579">
+        <v>40</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -18783,10 +19479,19 @@
       <c r="F580">
         <v>0.6796333690605267</v>
       </c>
+      <c r="G580">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H580">
+        <v>0.7076147166818574</v>
+      </c>
+      <c r="I580">
+        <v>14</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -18807,10 +19512,19 @@
       <c r="F581">
         <v>0.700370091056468</v>
       </c>
+      <c r="G581">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H581">
+        <v>0.7292051952075838</v>
+      </c>
+      <c r="I581">
+        <v>17</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -18831,10 +19545,19 @@
       <c r="F582">
         <v>1.38842927040198</v>
       </c>
+      <c r="G582">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H582">
+        <v>1.445592623220356</v>
+      </c>
+      <c r="I582">
+        <v>47</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -18855,10 +19578,19 @@
       <c r="F583">
         <v>0.7028487842852077</v>
       </c>
+      <c r="G583">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H583">
+        <v>0.7317859393067448</v>
+      </c>
+      <c r="I583">
+        <v>18</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -18879,10 +19611,19 @@
       <c r="F584">
         <v>0.891645867969482</v>
       </c>
+      <c r="G584">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H584">
+        <v>0.9283560327768183</v>
+      </c>
+      <c r="I584">
+        <v>22</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -18903,10 +19644,19 @@
       <c r="F585">
         <v>0.3302821603137818</v>
       </c>
+      <c r="G585">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H585">
+        <v>0.3438802859526671</v>
+      </c>
+      <c r="I585">
+        <v>1</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -18927,10 +19677,19 @@
       <c r="F586">
         <v>0.687999405488645</v>
       </c>
+      <c r="G586">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H586">
+        <v>0.7163251931921798</v>
+      </c>
+      <c r="I586">
+        <v>15</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -18951,10 +19710,19 @@
       <c r="F587">
         <v>1.072860645259916</v>
       </c>
+      <c r="G587">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H587">
+        <v>1.117031646907113</v>
+      </c>
+      <c r="I587">
+        <v>37</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -18975,10 +19743,19 @@
       <c r="F588">
         <v>1.040451958710402</v>
       </c>
+      <c r="G588">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H588">
+        <v>1.083288654589849</v>
+      </c>
+      <c r="I588">
+        <v>34</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -18999,10 +19776,19 @@
       <c r="F589">
         <v>1.01980536865182</v>
       </c>
+      <c r="G589">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H589">
+        <v>1.061792018844983</v>
+      </c>
+      <c r="I589">
+        <v>30</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -19023,10 +19809,19 @@
       <c r="F590">
         <v>0.5037562395090401</v>
       </c>
+      <c r="G590">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H590">
+        <v>0.524496507859315</v>
+      </c>
+      <c r="I590">
+        <v>4</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -19047,10 +19842,19 @@
       <c r="F591">
         <v>1.310287011813789</v>
       </c>
+      <c r="G591">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H591">
+        <v>1.364233151056419</v>
+      </c>
+      <c r="I591">
+        <v>46</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -19071,10 +19875,19 @@
       <c r="F592">
         <v>0.5195600425309252</v>
       </c>
+      <c r="G592">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H592">
+        <v>0.5409509730267414</v>
+      </c>
+      <c r="I592">
+        <v>5</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -19089,10 +19902,13 @@
           <t>urban_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="G593">
+        <v>0.9604568037355969</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -19113,10 +19929,19 @@
       <c r="F594">
         <v>1.033397367658967</v>
       </c>
+      <c r="G594">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H594">
+        <v>1.075943617286769</v>
+      </c>
+      <c r="I594">
+        <v>33</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -19137,10 +19962,19 @@
       <c r="F595">
         <v>0.5521000077874636</v>
       </c>
+      <c r="G595">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H595">
+        <v>0.5748306489580042</v>
+      </c>
+      <c r="I595">
+        <v>7</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -19161,10 +19995,19 @@
       <c r="F596">
         <v>0.5689224355899444</v>
       </c>
+      <c r="G596">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H596">
+        <v>0.5923456769499468</v>
+      </c>
+      <c r="I596">
+        <v>8</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -19185,10 +20028,19 @@
       <c r="F597">
         <v>0.6701119199469469</v>
       </c>
+      <c r="G597">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H597">
+        <v>0.6977012577146793</v>
+      </c>
+      <c r="I597">
+        <v>12</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -19209,10 +20061,19 @@
       <c r="F598">
         <v>1.016886976352176</v>
       </c>
+      <c r="G598">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H598">
+        <v>1.058753472719543</v>
+      </c>
+      <c r="I598">
+        <v>29</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -19233,10 +20094,19 @@
       <c r="F599">
         <v>1.238794342396874</v>
       </c>
+      <c r="G599">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H599">
+        <v>1.289797039886346</v>
+      </c>
+      <c r="I599">
+        <v>44</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -19257,10 +20127,19 @@
       <c r="F600">
         <v>0.6403066259390674</v>
       </c>
+      <c r="G600">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H600">
+        <v>0.66666884283464</v>
+      </c>
+      <c r="I600">
+        <v>9</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -19281,10 +20160,19 @@
       <c r="F601">
         <v>1.051504159876637</v>
       </c>
+      <c r="G601">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="H601">
+        <v>1.094795888567732</v>
+      </c>
+      <c r="I601">
+        <v>35</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -19305,10 +20193,19 @@
       <c r="F602">
         <v>1.376907820757462</v>
       </c>
+      <c r="G602">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H602">
+        <v>0.950295253754483</v>
+      </c>
+      <c r="I602">
+        <v>29</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -19329,10 +20226,19 @@
       <c r="F603">
         <v>0.9856966282590103</v>
       </c>
+      <c r="G603">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H603">
+        <v>0.6802945072684946</v>
+      </c>
+      <c r="I603">
+        <v>7</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -19353,10 +20259,19 @@
       <c r="F604">
         <v>2.124589567809786</v>
       </c>
+      <c r="G604">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H604">
+        <v>1.466319932263327</v>
+      </c>
+      <c r="I604">
+        <v>49</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -19377,10 +20292,19 @@
       <c r="F605">
         <v>1.729944927007016</v>
       </c>
+      <c r="G605">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H605">
+        <v>1.19394953576997</v>
+      </c>
+      <c r="I605">
+        <v>42</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -19401,10 +20325,19 @@
       <c r="F606">
         <v>1.657149781407989</v>
       </c>
+      <c r="G606">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H606">
+        <v>1.143708785941803</v>
+      </c>
+      <c r="I606">
+        <v>39</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -19425,10 +20358,19 @@
       <c r="F607">
         <v>1.291920192878279</v>
       </c>
+      <c r="G607">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H607">
+        <v>0.8916396646265115</v>
+      </c>
+      <c r="I607">
+        <v>18</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -19449,10 +20391,19 @@
       <c r="F608">
         <v>1.453119341995307</v>
       </c>
+      <c r="G608">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H608">
+        <v>1.002893870613157</v>
+      </c>
+      <c r="I608">
+        <v>32</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -19473,10 +20424,19 @@
       <c r="F609">
         <v>1.619642869533952</v>
       </c>
+      <c r="G609">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H609">
+        <v>1.117822782681775</v>
+      </c>
+      <c r="I609">
+        <v>37</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -19497,10 +20457,19 @@
       <c r="F610">
         <v>1.192460724106906</v>
       </c>
+      <c r="G610">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H610">
+        <v>0.8229960999016175</v>
+      </c>
+      <c r="I610">
+        <v>14</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -19521,10 +20490,19 @@
       <c r="F611">
         <v>1.331335669055292</v>
       </c>
+      <c r="G611">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H611">
+        <v>0.9188428944802592</v>
+      </c>
+      <c r="I611">
+        <v>24</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -19545,10 +20523,19 @@
       <c r="F612">
         <v>0.6786476065228866</v>
       </c>
+      <c r="G612">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H612">
+        <v>0.4683796472996711</v>
+      </c>
+      <c r="I612">
+        <v>2</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -19569,10 +20556,19 @@
       <c r="F613">
         <v>1.293098669726099</v>
       </c>
+      <c r="G613">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H613">
+        <v>0.8924530095274993</v>
+      </c>
+      <c r="I613">
+        <v>19</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -19593,10 +20589,19 @@
       <c r="F614">
         <v>1.322136431171046</v>
       </c>
+      <c r="G614">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H614">
+        <v>0.9124938913242251</v>
+      </c>
+      <c r="I614">
+        <v>22</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -19617,10 +20622,19 @@
       <c r="F615">
         <v>1.028614968017167</v>
       </c>
+      <c r="G615">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H615">
+        <v>0.7099152952082147</v>
+      </c>
+      <c r="I615">
+        <v>10</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -19641,10 +20655,19 @@
       <c r="F616">
         <v>1.583484806397701</v>
       </c>
+      <c r="G616">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H616">
+        <v>1.09286770924452</v>
+      </c>
+      <c r="I616">
+        <v>34</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -19665,10 +20688,19 @@
       <c r="F617">
         <v>1.319627999780003</v>
       </c>
+      <c r="G617">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H617">
+        <v>0.9107626567351403</v>
+      </c>
+      <c r="I617">
+        <v>21</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -19689,10 +20721,19 @@
       <c r="F618">
         <v>1.942203917118805</v>
       </c>
+      <c r="G618">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H618">
+        <v>1.340443518757872</v>
+      </c>
+      <c r="I618">
+        <v>46</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -19713,10 +20754,19 @@
       <c r="F619">
         <v>1.613310347190545</v>
       </c>
+      <c r="G619">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H619">
+        <v>1.113452289729006</v>
+      </c>
+      <c r="I619">
+        <v>36</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -19737,10 +20787,19 @@
       <c r="F620">
         <v>1.374254424733155</v>
       </c>
+      <c r="G620">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H620">
+        <v>0.9484639694737076</v>
+      </c>
+      <c r="I620">
+        <v>28</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -19761,10 +20820,19 @@
       <c r="F621">
         <v>1.116408646892007</v>
       </c>
+      <c r="G621">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H621">
+        <v>0.7705075259201506</v>
+      </c>
+      <c r="I621">
+        <v>12</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -19785,10 +20853,19 @@
       <c r="F622">
         <v>0.6589473424623987</v>
       </c>
+      <c r="G622">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H622">
+        <v>0.4547831906943969</v>
+      </c>
+      <c r="I622">
+        <v>1</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -19809,10 +20886,19 @@
       <c r="F623">
         <v>1.367814752575387</v>
       </c>
+      <c r="G623">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H623">
+        <v>0.944019525339535</v>
+      </c>
+      <c r="I623">
+        <v>27</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -19833,10 +20919,19 @@
       <c r="F624">
         <v>0.9749327334081804</v>
       </c>
+      <c r="G624">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H624">
+        <v>0.6728656307420843</v>
+      </c>
+      <c r="I624">
+        <v>6</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -19857,10 +20952,19 @@
       <c r="F625">
         <v>1.885996081543883</v>
       </c>
+      <c r="G625">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H625">
+        <v>1.301650769842206</v>
+      </c>
+      <c r="I625">
+        <v>43</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -19881,10 +20985,19 @@
       <c r="F626">
         <v>1.016119235271226</v>
       </c>
+      <c r="G626">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H626">
+        <v>0.7012911626834096</v>
+      </c>
+      <c r="I626">
+        <v>9</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -19905,10 +21018,19 @@
       <c r="F627">
         <v>1.685846434514267</v>
       </c>
+      <c r="G627">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H627">
+        <v>1.163514246288838</v>
+      </c>
+      <c r="I627">
+        <v>40</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -19929,10 +21051,19 @@
       <c r="F628">
         <v>1.326307566181995</v>
       </c>
+      <c r="G628">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H628">
+        <v>0.9153726677709252</v>
+      </c>
+      <c r="I628">
+        <v>23</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -19953,10 +21084,19 @@
       <c r="F629">
         <v>1.45342616195017</v>
       </c>
+      <c r="G629">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H629">
+        <v>1.00310562737891</v>
+      </c>
+      <c r="I629">
+        <v>33</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -19977,10 +21117,19 @@
       <c r="F630">
         <v>1.197246280140075</v>
       </c>
+      <c r="G630">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H630">
+        <v>0.8262989289772738</v>
+      </c>
+      <c r="I630">
+        <v>16</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -20001,10 +21150,19 @@
       <c r="F631">
         <v>0.9487930017384785</v>
       </c>
+      <c r="G631">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H631">
+        <v>0.6548248711751378</v>
+      </c>
+      <c r="I631">
+        <v>5</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -20025,10 +21183,19 @@
       <c r="F632">
         <v>1.312811911777458</v>
       </c>
+      <c r="G632">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H632">
+        <v>0.9060584231035613</v>
+      </c>
+      <c r="I632">
+        <v>20</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -20049,10 +21216,19 @@
       <c r="F633">
         <v>1.194541570937952</v>
       </c>
+      <c r="G633">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H633">
+        <v>0.8244322300749829</v>
+      </c>
+      <c r="I633">
+        <v>15</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -20073,10 +21249,19 @@
       <c r="F634">
         <v>1.429086850448325</v>
       </c>
+      <c r="G634">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H634">
+        <v>0.98630745697769</v>
+      </c>
+      <c r="I634">
+        <v>30</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -20097,10 +21282,19 @@
       <c r="F635">
         <v>1.086157823037984</v>
       </c>
+      <c r="G635">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H635">
+        <v>0.7496294294366646</v>
+      </c>
+      <c r="I635">
+        <v>11</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -20121,10 +21315,19 @@
       <c r="F636">
         <v>1.346999624977847</v>
       </c>
+      <c r="G636">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H636">
+        <v>0.9296536275909441</v>
+      </c>
+      <c r="I636">
+        <v>26</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -20145,10 +21348,19 @@
       <c r="F637">
         <v>1.892020534142045</v>
       </c>
+      <c r="G637">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H637">
+        <v>1.30580864346613</v>
+      </c>
+      <c r="I637">
+        <v>44</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -20169,10 +21381,19 @@
       <c r="F638">
         <v>1.625212381849401</v>
       </c>
+      <c r="G638">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H638">
+        <v>1.12166667189448</v>
+      </c>
+      <c r="I638">
+        <v>38</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -20193,10 +21414,19 @@
       <c r="F639">
         <v>1.603578005470747</v>
       </c>
+      <c r="G639">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H639">
+        <v>1.10673535631864</v>
+      </c>
+      <c r="I639">
+        <v>35</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -20217,10 +21447,19 @@
       <c r="F640">
         <v>0.9291123786127875</v>
       </c>
+      <c r="G640">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H640">
+        <v>0.6412419700794157</v>
+      </c>
+      <c r="I640">
+        <v>4</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -20241,10 +21480,19 @@
       <c r="F641">
         <v>1.911937498862678</v>
       </c>
+      <c r="G641">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H641">
+        <v>1.319554659544971</v>
+      </c>
+      <c r="I641">
+        <v>45</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -20265,10 +21513,19 @@
       <c r="F642">
         <v>2.023549657207091</v>
       </c>
+      <c r="G642">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H642">
+        <v>1.396585599987767</v>
+      </c>
+      <c r="I642">
+        <v>47</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -20283,10 +21540,13 @@
           <t>other_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="G643">
+        <v>1.44892633664905</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -20307,10 +21567,19 @@
       <c r="F644">
         <v>1.722212539357844</v>
       </c>
+      <c r="G644">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H644">
+        <v>1.188612903083</v>
+      </c>
+      <c r="I644">
+        <v>41</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -20331,10 +21600,19 @@
       <c r="F645">
         <v>0.8086699302884396</v>
       </c>
+      <c r="G645">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H645">
+        <v>0.5581166618578144</v>
+      </c>
+      <c r="I645">
+        <v>3</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -20355,10 +21633,19 @@
       <c r="F646">
         <v>0.9951797232199359</v>
       </c>
+      <c r="G646">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H646">
+        <v>0.6868394189876488</v>
+      </c>
+      <c r="I646">
+        <v>8</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -20379,10 +21666,19 @@
       <c r="F647">
         <v>1.332223226835592</v>
       </c>
+      <c r="G647">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H647">
+        <v>0.9194554568706659</v>
+      </c>
+      <c r="I647">
+        <v>25</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -20403,10 +21699,19 @@
       <c r="F648">
         <v>1.452483884490658</v>
       </c>
+      <c r="G648">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H648">
+        <v>1.002455299314826</v>
+      </c>
+      <c r="I648">
+        <v>31</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -20427,10 +21732,19 @@
       <c r="F649">
         <v>2.078509820622562</v>
       </c>
+      <c r="G649">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H649">
+        <v>1.434517247736388</v>
+      </c>
+      <c r="I649">
+        <v>48</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -20451,10 +21765,19 @@
       <c r="F650">
         <v>1.176024938556992</v>
       </c>
+      <c r="G650">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H650">
+        <v>0.8116526760613654</v>
+      </c>
+      <c r="I650">
+        <v>13</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -20474,6 +21797,15 @@
       </c>
       <c r="F651">
         <v>1.266123223323891</v>
+      </c>
+      <c r="G651">
+        <v>1.44892633664905</v>
+      </c>
+      <c r="H651">
+        <v>0.8738354678900174</v>
+      </c>
+      <c r="I651">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -20515,7 +21847,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -20534,7 +21866,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -20553,7 +21885,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -20572,7 +21904,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -20591,7 +21923,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -20610,7 +21942,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -20629,7 +21961,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -20648,7 +21980,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -20667,7 +21999,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -20686,7 +22018,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -20705,7 +22037,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -20724,7 +22056,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -20743,7 +22075,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -20762,7 +22094,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -20781,7 +22113,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -20800,7 +22132,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -20819,7 +22151,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -20838,7 +22170,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -20857,7 +22189,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -20876,7 +22208,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -20895,7 +22227,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -20914,7 +22246,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -20933,7 +22265,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -20952,7 +22284,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -20971,7 +22303,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -20990,7 +22322,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -21009,7 +22341,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -21028,7 +22360,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -21047,7 +22379,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -21066,7 +22398,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -21085,7 +22417,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -21104,7 +22436,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -21123,7 +22455,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -21142,7 +22474,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -21161,7 +22493,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -21180,7 +22512,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -21199,7 +22531,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -21218,7 +22550,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -21237,7 +22569,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -21256,7 +22588,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -21275,7 +22607,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -21294,7 +22626,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -21313,7 +22645,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -21332,7 +22664,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -21351,7 +22683,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -21370,7 +22702,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -21389,7 +22721,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -21408,7 +22740,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -21427,7 +22759,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -21446,7 +22778,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -21465,7 +22797,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -21576,7 +22908,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -21616,10 +22948,19 @@
       <c r="M2">
         <v>9</v>
       </c>
+      <c r="N2">
+        <v>41</v>
+      </c>
+      <c r="O2">
+        <v>36</v>
+      </c>
+      <c r="P2">
+        <v>29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -21659,10 +23000,19 @@
       <c r="M3">
         <v>36</v>
       </c>
+      <c r="N3">
+        <v>48</v>
+      </c>
+      <c r="O3">
+        <v>45</v>
+      </c>
+      <c r="P3">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -21670,7 +23020,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>32</v>
@@ -21702,10 +23052,19 @@
       <c r="M4">
         <v>2</v>
       </c>
+      <c r="N4">
+        <v>39</v>
+      </c>
+      <c r="O4">
+        <v>43</v>
+      </c>
+      <c r="P4">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -21713,7 +23072,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>24</v>
@@ -21745,10 +23104,19 @@
       <c r="M5">
         <v>22</v>
       </c>
+      <c r="N5">
+        <v>47</v>
+      </c>
+      <c r="O5">
+        <v>26</v>
+      </c>
+      <c r="P5">
+        <v>42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -21756,7 +23124,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>42</v>
@@ -21788,10 +23156,19 @@
       <c r="M6">
         <v>24</v>
       </c>
+      <c r="N6">
+        <v>30</v>
+      </c>
+      <c r="O6">
+        <v>23</v>
+      </c>
+      <c r="P6">
+        <v>39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -21831,10 +23208,19 @@
       <c r="M7">
         <v>18</v>
       </c>
+      <c r="N7">
+        <v>35</v>
+      </c>
+      <c r="O7">
+        <v>41</v>
+      </c>
+      <c r="P7">
+        <v>18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -21842,7 +23228,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>19</v>
@@ -21874,10 +23260,19 @@
       <c r="M8">
         <v>16</v>
       </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8">
+        <v>32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -21885,7 +23280,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -21914,10 +23309,19 @@
       <c r="M9">
         <v>4</v>
       </c>
+      <c r="N9">
+        <v>18</v>
+      </c>
+      <c r="O9">
+        <v>27</v>
+      </c>
+      <c r="P9">
+        <v>37</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -21925,7 +23329,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>38</v>
@@ -21957,10 +23361,19 @@
       <c r="M10">
         <v>6</v>
       </c>
+      <c r="N10">
+        <v>40</v>
+      </c>
+      <c r="O10">
+        <v>39</v>
+      </c>
+      <c r="P10">
+        <v>14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -21968,7 +23381,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11">
         <v>20</v>
@@ -22000,10 +23413,19 @@
       <c r="M11">
         <v>5</v>
       </c>
+      <c r="N11">
+        <v>13</v>
+      </c>
+      <c r="O11">
+        <v>32</v>
+      </c>
+      <c r="P11">
+        <v>24</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -22011,7 +23433,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -22043,10 +23465,19 @@
       <c r="M12">
         <v>30</v>
       </c>
+      <c r="N12">
+        <v>49</v>
+      </c>
+      <c r="O12">
+        <v>38</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -22054,7 +23485,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>49</v>
@@ -22086,10 +23517,19 @@
       <c r="M13">
         <v>19</v>
       </c>
+      <c r="N13">
+        <v>38</v>
+      </c>
+      <c r="O13">
+        <v>11</v>
+      </c>
+      <c r="P13">
+        <v>19</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -22129,10 +23569,19 @@
       <c r="M14">
         <v>40</v>
       </c>
+      <c r="N14">
+        <v>20</v>
+      </c>
+      <c r="O14">
+        <v>25</v>
+      </c>
+      <c r="P14">
+        <v>22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -22140,7 +23589,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D15">
         <v>47</v>
@@ -22172,10 +23621,19 @@
       <c r="M15">
         <v>20</v>
       </c>
+      <c r="N15">
+        <v>25</v>
+      </c>
+      <c r="O15">
+        <v>16</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -22183,7 +23641,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16">
         <v>39</v>
@@ -22215,10 +23673,19 @@
       <c r="M16">
         <v>50</v>
       </c>
+      <c r="N16">
+        <v>8</v>
+      </c>
+      <c r="O16">
+        <v>10</v>
+      </c>
+      <c r="P16">
+        <v>34</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -22226,7 +23693,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17">
         <v>44</v>
@@ -22258,10 +23725,19 @@
       <c r="M17">
         <v>21</v>
       </c>
+      <c r="N17">
+        <v>17</v>
+      </c>
+      <c r="O17">
+        <v>13</v>
+      </c>
+      <c r="P17">
+        <v>21</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -22269,7 +23745,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>14</v>
@@ -22301,10 +23777,19 @@
       <c r="M18">
         <v>33</v>
       </c>
+      <c r="N18">
+        <v>23</v>
+      </c>
+      <c r="O18">
+        <v>24</v>
+      </c>
+      <c r="P18">
+        <v>46</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -22344,10 +23829,19 @@
       <c r="M19">
         <v>44</v>
       </c>
+      <c r="N19">
+        <v>22</v>
+      </c>
+      <c r="O19">
+        <v>42</v>
+      </c>
+      <c r="P19">
+        <v>36</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -22355,7 +23849,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D20">
         <v>23</v>
@@ -22387,10 +23881,19 @@
       <c r="M20">
         <v>47</v>
       </c>
+      <c r="N20">
+        <v>28</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <v>28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -22398,7 +23901,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21">
         <v>37</v>
@@ -22430,10 +23933,19 @@
       <c r="M21">
         <v>14</v>
       </c>
+      <c r="N21">
+        <v>7</v>
+      </c>
+      <c r="O21">
+        <v>28</v>
+      </c>
+      <c r="P21">
+        <v>12</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -22441,7 +23953,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -22473,10 +23985,19 @@
       <c r="M22">
         <v>38</v>
       </c>
+      <c r="N22">
+        <v>11</v>
+      </c>
+      <c r="O22">
+        <v>6</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -22484,7 +24005,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D23">
         <v>30</v>
@@ -22516,10 +24037,19 @@
       <c r="M23">
         <v>43</v>
       </c>
+      <c r="N23">
+        <v>12</v>
+      </c>
+      <c r="O23">
+        <v>21</v>
+      </c>
+      <c r="P23">
+        <v>27</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -22527,7 +24057,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D24">
         <v>25</v>
@@ -22559,10 +24089,19 @@
       <c r="M24">
         <v>12</v>
       </c>
+      <c r="N24">
+        <v>15</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="P24">
+        <v>6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -22570,7 +24109,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D25">
         <v>16</v>
@@ -22602,10 +24141,19 @@
       <c r="M25">
         <v>26</v>
       </c>
+      <c r="N25">
+        <v>43</v>
+      </c>
+      <c r="O25">
+        <v>49</v>
+      </c>
+      <c r="P25">
+        <v>43</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -22645,10 +24193,19 @@
       <c r="M26">
         <v>39</v>
       </c>
+      <c r="N26">
+        <v>24</v>
+      </c>
+      <c r="O26">
+        <v>31</v>
+      </c>
+      <c r="P26">
+        <v>9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -22656,7 +24213,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D27">
         <v>18</v>
@@ -22688,10 +24245,19 @@
       <c r="M27">
         <v>32</v>
       </c>
+      <c r="N27">
+        <v>34</v>
+      </c>
+      <c r="O27">
+        <v>48</v>
+      </c>
+      <c r="P27">
+        <v>40</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -22699,7 +24265,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D28">
         <v>26</v>
@@ -22731,10 +24297,19 @@
       <c r="M28">
         <v>37</v>
       </c>
+      <c r="N28">
+        <v>29</v>
+      </c>
+      <c r="O28">
+        <v>20</v>
+      </c>
+      <c r="P28">
+        <v>23</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -22742,7 +24317,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D29">
         <v>46</v>
@@ -22774,10 +24349,19 @@
       <c r="M29">
         <v>1</v>
       </c>
+      <c r="N29">
+        <v>36</v>
+      </c>
+      <c r="O29">
+        <v>40</v>
+      </c>
+      <c r="P29">
+        <v>33</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -22785,7 +24369,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -22817,10 +24401,19 @@
       <c r="M30">
         <v>34</v>
       </c>
+      <c r="N30">
+        <v>16</v>
+      </c>
+      <c r="O30">
+        <v>14</v>
+      </c>
+      <c r="P30">
+        <v>16</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -22828,7 +24421,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31">
         <v>45</v>
@@ -22860,10 +24453,19 @@
       <c r="M31">
         <v>25</v>
       </c>
+      <c r="N31">
+        <v>46</v>
+      </c>
+      <c r="O31">
+        <v>17</v>
+      </c>
+      <c r="P31">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -22871,7 +24473,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D32">
         <v>13</v>
@@ -22903,10 +24505,19 @@
       <c r="M32">
         <v>13</v>
       </c>
+      <c r="N32">
+        <v>42</v>
+      </c>
+      <c r="O32">
+        <v>47</v>
+      </c>
+      <c r="P32">
+        <v>20</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -22914,7 +24525,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33">
         <v>31</v>
@@ -22946,10 +24557,19 @@
       <c r="M33">
         <v>41</v>
       </c>
+      <c r="N33">
+        <v>4</v>
+      </c>
+      <c r="O33">
+        <v>18</v>
+      </c>
+      <c r="P33">
+        <v>15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -22957,7 +24577,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -22989,10 +24609,19 @@
       <c r="M34">
         <v>31</v>
       </c>
+      <c r="N34">
+        <v>31</v>
+      </c>
+      <c r="O34">
+        <v>22</v>
+      </c>
+      <c r="P34">
+        <v>30</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -23000,7 +24629,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>33</v>
@@ -23032,10 +24661,19 @@
       <c r="M35">
         <v>42</v>
       </c>
+      <c r="N35">
+        <v>14</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>11</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -23043,7 +24681,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>11</v>
@@ -23075,10 +24713,19 @@
       <c r="M36">
         <v>17</v>
       </c>
+      <c r="N36">
+        <v>9</v>
+      </c>
+      <c r="O36">
+        <v>15</v>
+      </c>
+      <c r="P36">
+        <v>26</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -23086,7 +24733,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D37">
         <v>40</v>
@@ -23118,10 +24765,19 @@
       <c r="M37">
         <v>35</v>
       </c>
+      <c r="N37">
+        <v>21</v>
+      </c>
+      <c r="O37">
+        <v>37</v>
+      </c>
+      <c r="P37">
+        <v>44</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -23129,7 +24785,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D38">
         <v>28</v>
@@ -23161,10 +24817,19 @@
       <c r="M38">
         <v>15</v>
       </c>
+      <c r="N38">
+        <v>44</v>
+      </c>
+      <c r="O38">
+        <v>34</v>
+      </c>
+      <c r="P38">
+        <v>38</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -23204,10 +24869,19 @@
       <c r="M39">
         <v>45</v>
       </c>
+      <c r="N39">
+        <v>6</v>
+      </c>
+      <c r="O39">
+        <v>30</v>
+      </c>
+      <c r="P39">
+        <v>35</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -23215,7 +24889,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D40">
         <v>27</v>
@@ -23247,10 +24921,19 @@
       <c r="M40">
         <v>46</v>
       </c>
+      <c r="N40">
+        <v>5</v>
+      </c>
+      <c r="O40">
+        <v>4</v>
+      </c>
+      <c r="P40">
+        <v>4</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -23258,7 +24941,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -23290,10 +24973,19 @@
       <c r="M41">
         <v>27</v>
       </c>
+      <c r="N41">
+        <v>45</v>
+      </c>
+      <c r="O41">
+        <v>46</v>
+      </c>
+      <c r="P41">
+        <v>45</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -23301,7 +24993,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>34</v>
@@ -23333,10 +25025,19 @@
       <c r="M42">
         <v>48</v>
       </c>
+      <c r="N42">
+        <v>27</v>
+      </c>
+      <c r="O42">
+        <v>5</v>
+      </c>
+      <c r="P42">
+        <v>47</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -23344,7 +25045,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D43">
         <v>12</v>
@@ -23379,7 +25080,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -23387,7 +25088,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D44">
         <v>41</v>
@@ -23419,10 +25120,19 @@
       <c r="M44">
         <v>3</v>
       </c>
+      <c r="N44">
+        <v>37</v>
+      </c>
+      <c r="O44">
+        <v>33</v>
+      </c>
+      <c r="P44">
+        <v>41</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -23430,7 +25140,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D45">
         <v>43</v>
@@ -23462,10 +25172,19 @@
       <c r="M45">
         <v>8</v>
       </c>
+      <c r="N45">
+        <v>32</v>
+      </c>
+      <c r="O45">
+        <v>7</v>
+      </c>
+      <c r="P45">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -23473,7 +25192,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D46">
         <v>29</v>
@@ -23505,10 +25224,19 @@
       <c r="M46">
         <v>7</v>
       </c>
+      <c r="N46">
+        <v>2</v>
+      </c>
+      <c r="O46">
+        <v>8</v>
+      </c>
+      <c r="P46">
+        <v>8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -23516,7 +25244,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -23548,10 +25276,19 @@
       <c r="M47">
         <v>10</v>
       </c>
+      <c r="N47">
+        <v>33</v>
+      </c>
+      <c r="O47">
+        <v>12</v>
+      </c>
+      <c r="P47">
+        <v>25</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -23591,10 +25328,19 @@
       <c r="M48">
         <v>23</v>
       </c>
+      <c r="N48">
+        <v>26</v>
+      </c>
+      <c r="O48">
+        <v>29</v>
+      </c>
+      <c r="P48">
+        <v>31</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -23602,7 +25348,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D49">
         <v>9</v>
@@ -23634,10 +25380,19 @@
       <c r="M49">
         <v>49</v>
       </c>
+      <c r="N49">
+        <v>10</v>
+      </c>
+      <c r="O49">
+        <v>44</v>
+      </c>
+      <c r="P49">
+        <v>48</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -23645,7 +25400,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D50">
         <v>22</v>
@@ -23677,10 +25432,19 @@
       <c r="M50">
         <v>29</v>
       </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>9</v>
+      </c>
+      <c r="P50">
+        <v>13</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -23688,7 +25452,7 @@
         </is>
       </c>
       <c r="C51">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D51">
         <v>21</v>
@@ -23719,6 +25483,15 @@
       </c>
       <c r="M51">
         <v>28</v>
+      </c>
+      <c r="N51">
+        <v>19</v>
+      </c>
+      <c r="O51">
+        <v>35</v>
+      </c>
+      <c r="P51">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/AHR 30th/AHR_data 30th dashboard.xlsx
+++ b/AHR 30th/AHR_data 30th dashboard.xlsx
@@ -16918,13 +16918,13 @@
         <v>1.546558739611991</v>
       </c>
       <c r="G502">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H502">
-        <v>1.343662560004414</v>
+        <v>1.386367951805704</v>
       </c>
       <c r="I502">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="503">
@@ -16951,13 +16951,13 @@
         <v>1.916588853159228</v>
       </c>
       <c r="G503">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H503">
-        <v>1.665147672023079</v>
+        <v>1.718070768831341</v>
       </c>
       <c r="I503">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="504">
@@ -16984,13 +16984,13 @@
         <v>1.437964708203125</v>
       </c>
       <c r="G504">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H504">
-        <v>1.249315199954809</v>
+        <v>1.289021966136641</v>
       </c>
       <c r="I504">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="505">
@@ -17017,13 +17017,13 @@
         <v>1.791750853497073</v>
       </c>
       <c r="G505">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H505">
-        <v>1.556687422880544</v>
+        <v>1.606163346587189</v>
       </c>
       <c r="I505">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="506">
@@ -17050,13 +17050,13 @@
         <v>1.158444012988471</v>
       </c>
       <c r="G506">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H506">
-        <v>1.006465391999526</v>
+        <v>1.03845370527041</v>
       </c>
       <c r="I506">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="507">
@@ -17083,13 +17083,13 @@
         <v>1.323958484081296</v>
       </c>
       <c r="G507">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H507">
-        <v>1.150265683737659</v>
+        <v>1.186824376494145</v>
       </c>
       <c r="I507">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="508">
@@ -17116,10 +17116,10 @@
         <v>0.557401017424077</v>
       </c>
       <c r="G508">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H508">
-        <v>0.484274446768833</v>
+        <v>0.4996660566895171</v>
       </c>
       <c r="I508">
         <v>3</v>
@@ -17149,10 +17149,10 @@
         <v>0.9435103377597176</v>
       </c>
       <c r="G509">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H509">
-        <v>0.8197293018064832</v>
+        <v>0.8457826146297031</v>
       </c>
       <c r="I509">
         <v>18</v>
@@ -17182,13 +17182,13 @@
         <v>1.54518544526613</v>
       </c>
       <c r="G510">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H510">
-        <v>1.342469430930725</v>
+        <v>1.385136901719643</v>
       </c>
       <c r="I510">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="511">
@@ -17215,10 +17215,10 @@
         <v>0.8306768720704029</v>
       </c>
       <c r="G511">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H511">
-        <v>0.7216986874631109</v>
+        <v>0.7446363104407784</v>
       </c>
       <c r="I511">
         <v>13</v>
@@ -17248,13 +17248,13 @@
         <v>3.143211060938769</v>
       </c>
       <c r="G512">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H512">
-        <v>2.730846823079459</v>
+        <v>2.817640849347879</v>
       </c>
       <c r="I512">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="513">
@@ -17281,13 +17281,13 @@
         <v>1.424057155134427</v>
       </c>
       <c r="G513">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H513">
-        <v>1.237232206996926</v>
+        <v>1.276554941529921</v>
       </c>
       <c r="I513">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="514">
@@ -17314,10 +17314,10 @@
         <v>0.9563043256849029</v>
       </c>
       <c r="G514">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H514">
-        <v>0.8308448204918795</v>
+        <v>0.8572514158985873</v>
       </c>
       <c r="I514">
         <v>20</v>
@@ -17347,13 +17347,13 @@
         <v>1.042099344822047</v>
       </c>
       <c r="G515">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H515">
-        <v>0.9053842169575864</v>
+        <v>0.9341598849465423</v>
       </c>
       <c r="I515">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="516">
@@ -17380,10 +17380,10 @@
         <v>0.64135605439773</v>
       </c>
       <c r="G516">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H516">
-        <v>0.5572152520651036</v>
+        <v>0.5749251268248918</v>
       </c>
       <c r="I516">
         <v>8</v>
@@ -17413,10 +17413,10 @@
         <v>0.9315724843391602</v>
       </c>
       <c r="G517">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H517">
-        <v>0.809357599602629</v>
+        <v>0.8350812704313139</v>
       </c>
       <c r="I517">
         <v>17</v>
@@ -17446,13 +17446,13 @@
         <v>1.023625905976862</v>
       </c>
       <c r="G518">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H518">
-        <v>0.8893343460441584</v>
+        <v>0.9175999037970177</v>
       </c>
       <c r="I518">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="519">
@@ -17479,13 +17479,13 @@
         <v>0.9691454880831557</v>
       </c>
       <c r="G519">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H519">
-        <v>0.8420013247354865</v>
+        <v>0.8687625053625003</v>
       </c>
       <c r="I519">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="520">
@@ -17512,13 +17512,13 @@
         <v>1.077728692938083</v>
       </c>
       <c r="G520">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H520">
-        <v>0.9363392785887356</v>
+        <v>0.9660987858797161</v>
       </c>
       <c r="I520">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="521">
@@ -17545,10 +17545,10 @@
         <v>0.5978690522960789</v>
       </c>
       <c r="G521">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H521">
-        <v>0.5194333980208908</v>
+        <v>0.535942458731107</v>
       </c>
       <c r="I521">
         <v>7</v>
@@ -17578,10 +17578,10 @@
         <v>0.7424728473967344</v>
       </c>
       <c r="G522">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H522">
-        <v>0.6450663277860074</v>
+        <v>0.6655683578982627</v>
       </c>
       <c r="I522">
         <v>11</v>
@@ -17611,10 +17611,10 @@
         <v>0.8125484229061878</v>
       </c>
       <c r="G523">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H523">
-        <v>0.7059485463342907</v>
+        <v>0.7283855853351079</v>
       </c>
       <c r="I523">
         <v>12</v>
@@ -17644,10 +17644,10 @@
         <v>0.8978072570646936</v>
       </c>
       <c r="G524">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H524">
-        <v>0.7800221010168312</v>
+        <v>0.8048134068320945</v>
       </c>
       <c r="I524">
         <v>15</v>
@@ -17677,13 +17677,13 @@
         <v>1.652932463280736</v>
       </c>
       <c r="G525">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H525">
-        <v>1.436080898992177</v>
+        <v>1.481723606674385</v>
       </c>
       <c r="I525">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="526">
@@ -17710,13 +17710,13 @@
         <v>1.038530651512329</v>
       </c>
       <c r="G526">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H526">
-        <v>0.9022837077654113</v>
+        <v>0.9309608328137686</v>
       </c>
       <c r="I526">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="527">
@@ -17743,13 +17743,13 @@
         <v>1.265166521633523</v>
       </c>
       <c r="G527">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H527">
-        <v>1.099186758154736</v>
+        <v>1.134122018365926</v>
       </c>
       <c r="I527">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="528">
@@ -17776,13 +17776,13 @@
         <v>1.158331431633449</v>
       </c>
       <c r="G528">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H528">
-        <v>1.00636758042094</v>
+        <v>1.038352784963554</v>
       </c>
       <c r="I528">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="529">
@@ -17809,13 +17809,13 @@
         <v>1.331149152665648</v>
       </c>
       <c r="G529">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H529">
-        <v>1.156512993917818</v>
+        <v>1.19327024383954</v>
       </c>
       <c r="I529">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="530">
@@ -17842,10 +17842,10 @@
         <v>0.8989784599538359</v>
       </c>
       <c r="G530">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H530">
-        <v>0.7810396514221293</v>
+        <v>0.8058632978636996</v>
       </c>
       <c r="I530">
         <v>16</v>
@@ -17875,13 +17875,13 @@
         <v>1.757109056582949</v>
       </c>
       <c r="G531">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H531">
-        <v>1.526590353605009</v>
+        <v>1.57510970743039</v>
       </c>
       <c r="I531">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="532">
@@ -17908,13 +17908,13 @@
         <v>1.621249915389613</v>
       </c>
       <c r="G532">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H532">
-        <v>1.408554848854871</v>
+        <v>1.45332270090677</v>
       </c>
       <c r="I532">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="533">
@@ -17941,10 +17941,10 @@
         <v>0.5653356515936899</v>
       </c>
       <c r="G533">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H533">
-        <v>0.4911681201793336</v>
+        <v>0.5067788305145926</v>
       </c>
       <c r="I533">
         <v>4</v>
@@ -17974,13 +17974,13 @@
         <v>1.176656778823377</v>
       </c>
       <c r="G534">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H534">
-        <v>1.022288788123899</v>
+        <v>1.054780013622326</v>
       </c>
       <c r="I534">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="535">
@@ -18007,10 +18007,10 @@
         <v>0.8899499884751475</v>
       </c>
       <c r="G535">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H535">
-        <v>0.7731956434389442</v>
+        <v>0.7977699851486677</v>
       </c>
       <c r="I535">
         <v>14</v>
@@ -18040,10 +18040,10 @@
         <v>0.6690928544011803</v>
       </c>
       <c r="G536">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H536">
-        <v>0.5813132049875491</v>
+        <v>0.5997889807643001</v>
       </c>
       <c r="I536">
         <v>9</v>
@@ -18073,10 +18073,10 @@
         <v>0.9574745409619284</v>
       </c>
       <c r="G537">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H537">
-        <v>0.8318615128518986</v>
+        <v>0.8583004216138107</v>
       </c>
       <c r="I537">
         <v>21</v>
@@ -18106,13 +18106,13 @@
         <v>1.674049694553563</v>
       </c>
       <c r="G538">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H538">
-        <v>1.454427717839401</v>
+        <v>1.500653539251574</v>
       </c>
       <c r="I538">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="539">
@@ -18139,10 +18139,10 @@
         <v>0.5812995077504219</v>
       </c>
       <c r="G539">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H539">
-        <v>0.5050376456501077</v>
+        <v>0.5210891686841483</v>
       </c>
       <c r="I539">
         <v>6</v>
@@ -18172,10 +18172,10 @@
         <v>0.5727315192711556</v>
       </c>
       <c r="G540">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H540">
-        <v>0.4975937089671547</v>
+        <v>0.5134086426654111</v>
       </c>
       <c r="I540">
         <v>5</v>
@@ -18205,13 +18205,13 @@
         <v>1.732935271076938</v>
       </c>
       <c r="G541">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H541">
-        <v>1.505587976077368</v>
+        <v>1.553439815016368</v>
       </c>
       <c r="I541">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="542">
@@ -18238,13 +18238,13 @@
         <v>1.075570109353639</v>
       </c>
       <c r="G542">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H542">
-        <v>0.9344638839653246</v>
+        <v>0.9641637859174659</v>
       </c>
       <c r="I542">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="543">
@@ -18259,13 +18259,25 @@
       <c r="C543">
         <v>156</v>
       </c>
+      <c r="D543">
+        <v>16164.75063</v>
+      </c>
       <c r="E543" t="inlineStr">
         <is>
           <t>rural_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="F543">
+        <v>0.9650628306661357</v>
+      </c>
       <c r="G543">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
+      </c>
+      <c r="H543">
+        <v>0.8651027249376209</v>
+      </c>
+      <c r="I543">
+        <v>22</v>
       </c>
     </row>
     <row r="544">
@@ -18292,13 +18304,13 @@
         <v>1.337922335752768</v>
       </c>
       <c r="G544">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H544">
-        <v>1.162397589370366</v>
+        <v>1.199341868358666</v>
       </c>
       <c r="I544">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="545">
@@ -18325,13 +18337,13 @@
         <v>1.180604144687008</v>
       </c>
       <c r="G545">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H545">
-        <v>1.025718291049169</v>
+        <v>1.05831851583839</v>
       </c>
       <c r="I545">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="546">
@@ -18358,10 +18370,10 @@
         <v>0.5408658706973106</v>
       </c>
       <c r="G546">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H546">
-        <v>0.4699085794972739</v>
+        <v>0.4848436015746567</v>
       </c>
       <c r="I546">
         <v>2</v>
@@ -18391,13 +18403,13 @@
         <v>1.25354972894032</v>
       </c>
       <c r="G547">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H547">
-        <v>1.089093996069861</v>
+        <v>1.12370847979146</v>
       </c>
       <c r="I547">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="548">
@@ -18424,13 +18436,13 @@
         <v>1.053732927431458</v>
       </c>
       <c r="G548">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H548">
-        <v>0.9154915662554906</v>
+        <v>0.9445884743568733</v>
       </c>
       <c r="I548">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="549">
@@ -18457,10 +18469,10 @@
         <v>0.711916799512206</v>
       </c>
       <c r="G549">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H549">
-        <v>0.6185189898333322</v>
+        <v>0.6381772705532205</v>
       </c>
       <c r="I549">
         <v>10</v>
@@ -18490,10 +18502,10 @@
         <v>0.4906469365723513</v>
       </c>
       <c r="G550">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H550">
-        <v>0.4262779692535499</v>
+        <v>0.4398262872874848</v>
       </c>
       <c r="I550">
         <v>1</v>
@@ -18523,10 +18535,10 @@
         <v>0.9495847396975362</v>
       </c>
       <c r="G551">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H551">
-        <v>0.8250067906267997</v>
+        <v>0.8512278369528403</v>
       </c>
       <c r="I551">
         <v>19</v>
@@ -18556,10 +18568,10 @@
         <v>1.061679741146842</v>
       </c>
       <c r="G552">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H552">
-        <v>1.105390411122654</v>
+        <v>1.132780640519556</v>
       </c>
       <c r="I552">
         <v>36</v>
@@ -18589,10 +18601,10 @@
         <v>1.261411418464348</v>
       </c>
       <c r="G553">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H553">
-        <v>1.313345288989801</v>
+        <v>1.345888387229848</v>
       </c>
       <c r="I553">
         <v>45</v>
@@ -18622,10 +18634,10 @@
         <v>1.23537942968035</v>
       </c>
       <c r="G554">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H554">
-        <v>1.286241530983455</v>
+        <v>1.318113031078773</v>
       </c>
       <c r="I554">
         <v>43</v>
@@ -18655,10 +18667,10 @@
         <v>0.9822082835756718</v>
       </c>
       <c r="G555">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H555">
-        <v>1.022647015207217</v>
+        <v>1.04798696393188</v>
       </c>
       <c r="I555">
         <v>26</v>
@@ -18688,10 +18700,10 @@
         <v>0.9125068253040979</v>
       </c>
       <c r="G556">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H556">
-        <v>0.9500758615639947</v>
+        <v>0.9736175854027854</v>
       </c>
       <c r="I556">
         <v>23</v>
@@ -18721,10 +18733,10 @@
         <v>1.191299959746605</v>
       </c>
       <c r="G557">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H557">
-        <v>1.240347254674201</v>
+        <v>1.271081550444724</v>
       </c>
       <c r="I557">
         <v>41</v>
@@ -18754,10 +18766,10 @@
         <v>0.7196827190122299</v>
       </c>
       <c r="G558">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H558">
-        <v>0.7493129479775652</v>
+        <v>0.7678800110972188</v>
       </c>
       <c r="I558">
         <v>19</v>
@@ -18787,10 +18799,10 @@
         <v>0.9913191410168661</v>
       </c>
       <c r="G559">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H559">
-        <v>1.032132977934284</v>
+        <v>1.05770797727322</v>
       </c>
       <c r="I559">
         <v>27</v>
@@ -18820,10 +18832,10 @@
         <v>1.175569279528065</v>
       </c>
       <c r="G560">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H560">
-        <v>1.223968922866506</v>
+        <v>1.254297383503272</v>
       </c>
       <c r="I560">
         <v>39</v>
@@ -18853,10 +18865,10 @@
         <v>1.031157054593156</v>
       </c>
       <c r="G561">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H561">
-        <v>1.073611067757111</v>
+        <v>1.100213843693129</v>
       </c>
       <c r="I561">
         <v>32</v>
@@ -18886,10 +18898,10 @@
         <v>1.143791676866334</v>
       </c>
       <c r="G562">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H562">
-        <v>1.190882996942366</v>
+        <v>1.22039162859224</v>
       </c>
       <c r="I562">
         <v>38</v>
@@ -18919,10 +18931,10 @@
         <v>0.6697451321627513</v>
       </c>
       <c r="G563">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H563">
-        <v>0.6973193688230925</v>
+        <v>0.7145980943148119</v>
       </c>
       <c r="I563">
         <v>11</v>
@@ -18952,10 +18964,10 @@
         <v>0.9713350183635551</v>
       </c>
       <c r="G564">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H564">
-        <v>1.011326084198319</v>
+        <v>1.036385514027396</v>
       </c>
       <c r="I564">
         <v>25</v>
@@ -18985,10 +18997,10 @@
         <v>0.6881759063033738</v>
       </c>
       <c r="G565">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H565">
-        <v>0.7165089607640709</v>
+        <v>0.7342631809950314</v>
       </c>
       <c r="I565">
         <v>16</v>
@@ -19018,10 +19030,10 @@
         <v>0.6477854046018922</v>
       </c>
       <c r="G566">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H566">
-        <v>0.6744555320784841</v>
+        <v>0.6911677195153888</v>
       </c>
       <c r="I566">
         <v>10</v>
@@ -19051,10 +19063,10 @@
         <v>0.6714571986417301</v>
       </c>
       <c r="G567">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H567">
-        <v>0.6991019231996349</v>
+        <v>0.7164248182198708</v>
       </c>
       <c r="I567">
         <v>13</v>
@@ -19084,10 +19096,10 @@
         <v>0.9664382251635665</v>
       </c>
       <c r="G568">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H568">
-        <v>1.006227683956952</v>
+        <v>1.031160781631558</v>
       </c>
       <c r="I568">
         <v>24</v>
@@ -19117,10 +19129,10 @@
         <v>1.199541949337344</v>
       </c>
       <c r="G569">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H569">
-        <v>1.2489285771852</v>
+        <v>1.279875507686167</v>
       </c>
       <c r="I569">
         <v>42</v>
@@ -19150,10 +19162,10 @@
         <v>0.5028678933106425</v>
       </c>
       <c r="G570">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H570">
-        <v>0.5235715873475935</v>
+        <v>0.5365450542230532</v>
       </c>
       <c r="I570">
         <v>3</v>
@@ -19183,10 +19195,10 @@
         <v>1.011113274179578</v>
       </c>
       <c r="G571">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H571">
-        <v>1.052742060076994</v>
+        <v>1.078827727395196</v>
       </c>
       <c r="I571">
         <v>28</v>
@@ -19216,10 +19228,10 @@
         <v>0.5233313811194925</v>
       </c>
       <c r="G572">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H572">
-        <v>0.5448775822963089</v>
+        <v>0.5583789858023948</v>
       </c>
       <c r="I572">
         <v>6</v>
@@ -19249,10 +19261,10 @@
         <v>0.8461012176731455</v>
       </c>
       <c r="G573">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H573">
-        <v>0.8809362528146218</v>
+        <v>0.9027647812746559</v>
       </c>
       <c r="I573">
         <v>21</v>
@@ -19282,10 +19294,10 @@
         <v>0.3507276065045727</v>
       </c>
       <c r="G574">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H574">
-        <v>0.3651674964875611</v>
+        <v>0.3742159027306805</v>
       </c>
       <c r="I574">
         <v>2</v>
@@ -19315,13 +19327,13 @@
         <v>1.500817967161366</v>
       </c>
       <c r="G575">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H575">
-        <v>1.562608501833805</v>
+        <v>1.601328039195548</v>
       </c>
       <c r="I575">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="576">
@@ -19348,10 +19360,10 @@
         <v>1.023679431315542</v>
       </c>
       <c r="G576">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H576">
-        <v>1.065825581467118</v>
+        <v>1.09223544252591</v>
       </c>
       <c r="I576">
         <v>31</v>
@@ -19381,13 +19393,13 @@
         <v>1.446432915893151</v>
       </c>
       <c r="G577">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H577">
-        <v>1.505984350641695</v>
+        <v>1.543300810434689</v>
       </c>
       <c r="I577">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="578">
@@ -19414,10 +19426,10 @@
         <v>0.7859966683846932</v>
       </c>
       <c r="G578">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H578">
-        <v>0.8183571247844159</v>
+        <v>0.838635018595408</v>
       </c>
       <c r="I578">
         <v>20</v>
@@ -19447,10 +19459,10 @@
         <v>1.182648816398851</v>
       </c>
       <c r="G579">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H579">
-        <v>1.231339933039217</v>
+        <v>1.26185103833934</v>
       </c>
       <c r="I579">
         <v>40</v>
@@ -19480,10 +19492,10 @@
         <v>0.6796333690605267</v>
       </c>
       <c r="G580">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H580">
-        <v>0.7076147166818574</v>
+        <v>0.7251485483665879</v>
       </c>
       <c r="I580">
         <v>14</v>
@@ -19513,10 +19525,10 @@
         <v>0.700370091056468</v>
       </c>
       <c r="G581">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H581">
-        <v>0.7292051952075838</v>
+        <v>0.7472740126798316</v>
       </c>
       <c r="I581">
         <v>17</v>
@@ -19546,13 +19558,13 @@
         <v>1.38842927040198</v>
       </c>
       <c r="G582">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H582">
-        <v>1.445592623220356</v>
+        <v>1.481412649489863</v>
       </c>
       <c r="I582">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="583">
@@ -19579,10 +19591,10 @@
         <v>0.7028487842852077</v>
       </c>
       <c r="G583">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H583">
-        <v>0.7317859393067448</v>
+        <v>0.7499187044776333</v>
       </c>
       <c r="I583">
         <v>18</v>
@@ -19612,10 +19624,10 @@
         <v>0.891645867969482</v>
       </c>
       <c r="G584">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H584">
-        <v>0.9283560327768183</v>
+        <v>0.9513595656860007</v>
       </c>
       <c r="I584">
         <v>22</v>
@@ -19645,10 +19657,10 @@
         <v>0.3302821603137818</v>
       </c>
       <c r="G585">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H585">
-        <v>0.3438802859526671</v>
+        <v>0.3524012210200789</v>
       </c>
       <c r="I585">
         <v>1</v>
@@ -19678,10 +19690,10 @@
         <v>0.687999405488645</v>
       </c>
       <c r="G586">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H586">
-        <v>0.7163251931921798</v>
+        <v>0.7340748598863092</v>
       </c>
       <c r="I586">
         <v>15</v>
@@ -19711,10 +19723,10 @@
         <v>1.072860645259916</v>
       </c>
       <c r="G587">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H587">
-        <v>1.117031646907113</v>
+        <v>1.144710331962207</v>
       </c>
       <c r="I587">
         <v>37</v>
@@ -19744,10 +19756,10 @@
         <v>1.040451958710402</v>
       </c>
       <c r="G588">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H588">
-        <v>1.083288654589849</v>
+        <v>1.110131229352319</v>
       </c>
       <c r="I588">
         <v>34</v>
@@ -19777,10 +19789,10 @@
         <v>1.01980536865182</v>
       </c>
       <c r="G589">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H589">
-        <v>1.061792018844983</v>
+        <v>1.088101933129862</v>
       </c>
       <c r="I589">
         <v>30</v>
@@ -19810,10 +19822,10 @@
         <v>0.5037562395090401</v>
       </c>
       <c r="G590">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H590">
-        <v>0.524496507859315</v>
+        <v>0.5374928931396524</v>
       </c>
       <c r="I590">
         <v>4</v>
@@ -19843,13 +19855,13 @@
         <v>1.310287011813789</v>
       </c>
       <c r="G591">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H591">
-        <v>1.364233151056419</v>
+        <v>1.398037188600351</v>
       </c>
       <c r="I591">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="592">
@@ -19876,10 +19888,10 @@
         <v>0.5195600425309252</v>
       </c>
       <c r="G592">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H592">
-        <v>0.5409509730267414</v>
+        <v>0.5543550799328539</v>
       </c>
       <c r="I592">
         <v>5</v>
@@ -19897,13 +19909,25 @@
       <c r="C593">
         <v>415</v>
       </c>
+      <c r="D593">
+        <v>31959.74724</v>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>urban_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="F593">
+        <v>1.298508392083266</v>
+      </c>
       <c r="G593">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
+      </c>
+      <c r="H593">
+        <v>1.38546975240875</v>
+      </c>
+      <c r="I593">
+        <v>46</v>
       </c>
     </row>
     <row r="594">
@@ -19930,10 +19954,10 @@
         <v>1.033397367658967</v>
       </c>
       <c r="G594">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H594">
-        <v>1.075943617286769</v>
+        <v>1.102604190961989</v>
       </c>
       <c r="I594">
         <v>33</v>
@@ -19963,10 +19987,10 @@
         <v>0.5521000077874636</v>
       </c>
       <c r="G595">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H595">
-        <v>0.5748306489580042</v>
+        <v>0.589074253010385</v>
       </c>
       <c r="I595">
         <v>7</v>
@@ -19996,10 +20020,10 @@
         <v>0.5689224355899444</v>
       </c>
       <c r="G596">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H596">
-        <v>0.5923456769499468</v>
+        <v>0.6070232820844478</v>
       </c>
       <c r="I596">
         <v>8</v>
@@ -20029,10 +20053,10 @@
         <v>0.6701119199469469</v>
       </c>
       <c r="G597">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H597">
-        <v>0.6977012577146793</v>
+        <v>0.7149894459484665</v>
       </c>
       <c r="I597">
         <v>12</v>
@@ -20062,10 +20086,10 @@
         <v>1.016886976352176</v>
       </c>
       <c r="G598">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H598">
-        <v>1.058753472719543</v>
+        <v>1.084988095528603</v>
       </c>
       <c r="I598">
         <v>29</v>
@@ -20095,10 +20119,10 @@
         <v>1.238794342396874</v>
       </c>
       <c r="G599">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H599">
-        <v>1.289797039886346</v>
+        <v>1.32175664116609</v>
       </c>
       <c r="I599">
         <v>44</v>
@@ -20128,10 +20152,10 @@
         <v>0.6403066259390674</v>
       </c>
       <c r="G600">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H600">
-        <v>0.66666884283464</v>
+        <v>0.6831880855865854</v>
       </c>
       <c r="I600">
         <v>9</v>
@@ -20161,10 +20185,10 @@
         <v>1.051504159876637</v>
       </c>
       <c r="G601">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H601">
-        <v>1.094795888567732</v>
+        <v>1.121923598586675</v>
       </c>
       <c r="I601">
         <v>35</v>
@@ -20194,10 +20218,10 @@
         <v>1.376907820757462</v>
       </c>
       <c r="G602">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H602">
-        <v>0.950295253754483</v>
+        <v>0.9709932027434547</v>
       </c>
       <c r="I602">
         <v>29</v>
@@ -20227,10 +20251,10 @@
         <v>0.9856966282590103</v>
       </c>
       <c r="G603">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H603">
-        <v>0.6802945072684946</v>
+        <v>0.6951116927203739</v>
       </c>
       <c r="I603">
         <v>7</v>
@@ -20260,13 +20284,13 @@
         <v>2.124589567809786</v>
       </c>
       <c r="G604">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H604">
-        <v>1.466319932263327</v>
+        <v>1.498257180228726</v>
       </c>
       <c r="I604">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="605">
@@ -20293,10 +20317,10 @@
         <v>1.729944927007016</v>
       </c>
       <c r="G605">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H605">
-        <v>1.19394953576997</v>
+        <v>1.219954407928531</v>
       </c>
       <c r="I605">
         <v>42</v>
@@ -20326,10 +20350,10 @@
         <v>1.657149781407989</v>
       </c>
       <c r="G606">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H606">
-        <v>1.143708785941803</v>
+        <v>1.16861938716404</v>
       </c>
       <c r="I606">
         <v>39</v>
@@ -20359,10 +20383,10 @@
         <v>1.291920192878279</v>
       </c>
       <c r="G607">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H607">
-        <v>0.8916396646265115</v>
+        <v>0.9110600628891249</v>
       </c>
       <c r="I607">
         <v>18</v>
@@ -20392,10 +20416,10 @@
         <v>1.453119341995307</v>
       </c>
       <c r="G608">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H608">
-        <v>1.002893870613157</v>
+        <v>1.024737446168535</v>
       </c>
       <c r="I608">
         <v>32</v>
@@ -20425,10 +20449,10 @@
         <v>1.619642869533952</v>
       </c>
       <c r="G609">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H609">
-        <v>1.117822782681775</v>
+        <v>1.142169572632844</v>
       </c>
       <c r="I609">
         <v>37</v>
@@ -20458,10 +20482,10 @@
         <v>1.192460724106906</v>
       </c>
       <c r="G610">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H610">
-        <v>0.8229960999016175</v>
+        <v>0.8409214038811818</v>
       </c>
       <c r="I610">
         <v>14</v>
@@ -20491,10 +20515,10 @@
         <v>1.331335669055292</v>
       </c>
       <c r="G611">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H611">
-        <v>0.9188428944802592</v>
+        <v>0.9388557939277661</v>
       </c>
       <c r="I611">
         <v>24</v>
@@ -20524,10 +20548,10 @@
         <v>0.6786476065228866</v>
       </c>
       <c r="G612">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H612">
-        <v>0.4683796472996711</v>
+        <v>0.4785812115071946</v>
       </c>
       <c r="I612">
         <v>2</v>
@@ -20557,10 +20581,10 @@
         <v>1.293098669726099</v>
       </c>
       <c r="G613">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H613">
-        <v>0.8924530095274993</v>
+        <v>0.9118911228857154</v>
       </c>
       <c r="I613">
         <v>19</v>
@@ -20590,10 +20614,10 @@
         <v>1.322136431171046</v>
       </c>
       <c r="G614">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H614">
-        <v>0.9124938913242251</v>
+        <v>0.9323685060197717</v>
       </c>
       <c r="I614">
         <v>22</v>
@@ -20623,10 +20647,10 @@
         <v>1.028614968017167</v>
       </c>
       <c r="G615">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H615">
-        <v>0.7099152952082147</v>
+        <v>0.7253776375788172</v>
       </c>
       <c r="I615">
         <v>10</v>
@@ -20656,10 +20680,10 @@
         <v>1.583484806397701</v>
       </c>
       <c r="G616">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H616">
-        <v>1.09286770924452</v>
+        <v>1.116670964083759</v>
       </c>
       <c r="I616">
         <v>34</v>
@@ -20689,10 +20713,10 @@
         <v>1.319627999780003</v>
       </c>
       <c r="G617">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H617">
-        <v>0.9107626567351403</v>
+        <v>0.9305995641969917</v>
       </c>
       <c r="I617">
         <v>21</v>
@@ -20722,10 +20746,10 @@
         <v>1.942203917118805</v>
       </c>
       <c r="G618">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H618">
-        <v>1.340443518757872</v>
+        <v>1.369639109774699</v>
       </c>
       <c r="I618">
         <v>46</v>
@@ -20755,10 +20779,10 @@
         <v>1.613310347190545</v>
       </c>
       <c r="G619">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H619">
-        <v>1.113452289729006</v>
+        <v>1.137703887959569</v>
       </c>
       <c r="I619">
         <v>36</v>
@@ -20788,10 +20812,10 @@
         <v>1.374254424733155</v>
       </c>
       <c r="G620">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H620">
-        <v>0.9484639694737076</v>
+        <v>0.9691220320921243</v>
       </c>
       <c r="I620">
         <v>28</v>
@@ -20821,10 +20845,10 @@
         <v>1.116408646892007</v>
       </c>
       <c r="G621">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H621">
-        <v>0.7705075259201506</v>
+        <v>0.7872896001271995</v>
       </c>
       <c r="I621">
         <v>12</v>
@@ -20854,10 +20878,10 @@
         <v>0.6589473424623987</v>
       </c>
       <c r="G622">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H622">
-        <v>0.4547831906943969</v>
+        <v>0.4646886166605317</v>
       </c>
       <c r="I622">
         <v>1</v>
@@ -20887,10 +20911,10 @@
         <v>1.367814752575387</v>
       </c>
       <c r="G623">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H623">
-        <v>0.944019525339535</v>
+        <v>0.9645807855403769</v>
       </c>
       <c r="I623">
         <v>27</v>
@@ -20920,10 +20944,10 @@
         <v>0.9749327334081804</v>
       </c>
       <c r="G624">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H624">
-        <v>0.6728656307420843</v>
+        <v>0.6875210112109528</v>
       </c>
       <c r="I624">
         <v>6</v>
@@ -20953,10 +20977,10 @@
         <v>1.885996081543883</v>
       </c>
       <c r="G625">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H625">
-        <v>1.301650769842206</v>
+        <v>1.330001433627179</v>
       </c>
       <c r="I625">
         <v>43</v>
@@ -20986,10 +21010,10 @@
         <v>1.016119235271226</v>
       </c>
       <c r="G626">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H626">
-        <v>0.7012911626834096</v>
+        <v>0.7165656667433741</v>
       </c>
       <c r="I626">
         <v>9</v>
@@ -21019,10 +21043,10 @@
         <v>1.685846434514267</v>
       </c>
       <c r="G627">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H627">
-        <v>1.163514246288838</v>
+        <v>1.188856221240815</v>
       </c>
       <c r="I627">
         <v>40</v>
@@ -21052,10 +21076,10 @@
         <v>1.326307566181995</v>
       </c>
       <c r="G628">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H628">
-        <v>0.9153726677709252</v>
+        <v>0.9353099837877813</v>
       </c>
       <c r="I628">
         <v>23</v>
@@ -21085,10 +21109,10 @@
         <v>1.45342616195017</v>
       </c>
       <c r="G629">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H629">
-        <v>1.00310562737891</v>
+        <v>1.024953815112154</v>
       </c>
       <c r="I629">
         <v>33</v>
@@ -21118,10 +21142,10 @@
         <v>1.197246280140075</v>
       </c>
       <c r="G630">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H630">
-        <v>0.8262989289772738</v>
+        <v>0.8442961703757161</v>
       </c>
       <c r="I630">
         <v>16</v>
@@ -21151,10 +21175,10 @@
         <v>0.9487930017384785</v>
       </c>
       <c r="G631">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H631">
-        <v>0.6548248711751378</v>
+        <v>0.6690873140598569</v>
       </c>
       <c r="I631">
         <v>5</v>
@@ -21184,10 +21208,10 @@
         <v>1.312811911777458</v>
       </c>
       <c r="G632">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H632">
-        <v>0.9060584231035613</v>
+        <v>0.9257928697908755</v>
       </c>
       <c r="I632">
         <v>20</v>
@@ -21217,10 +21241,10 @@
         <v>1.194541570937952</v>
       </c>
       <c r="G633">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H633">
-        <v>0.8244322300749829</v>
+        <v>0.842388813753096</v>
       </c>
       <c r="I633">
         <v>15</v>
@@ -21250,10 +21274,10 @@
         <v>1.429086850448325</v>
       </c>
       <c r="G634">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H634">
-        <v>0.98630745697769</v>
+        <v>1.007789771396616</v>
       </c>
       <c r="I634">
         <v>30</v>
@@ -21283,10 +21307,10 @@
         <v>1.086157823037984</v>
       </c>
       <c r="G635">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H635">
-        <v>0.7496294294366646</v>
+        <v>0.7659567673138257</v>
       </c>
       <c r="I635">
         <v>11</v>
@@ -21316,10 +21340,10 @@
         <v>1.346999624977847</v>
       </c>
       <c r="G636">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H636">
-        <v>0.9296536275909441</v>
+        <v>0.9499019907025851</v>
       </c>
       <c r="I636">
         <v>26</v>
@@ -21349,10 +21373,10 @@
         <v>1.892020534142045</v>
       </c>
       <c r="G637">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H637">
-        <v>1.30580864346613</v>
+        <v>1.334249868006648</v>
       </c>
       <c r="I637">
         <v>44</v>
@@ -21382,10 +21406,10 @@
         <v>1.625212381849401</v>
       </c>
       <c r="G638">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H638">
-        <v>1.12166667189448</v>
+        <v>1.146097183849346</v>
       </c>
       <c r="I638">
         <v>38</v>
@@ -21415,10 +21439,10 @@
         <v>1.603578005470747</v>
       </c>
       <c r="G639">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H639">
-        <v>1.10673535631864</v>
+        <v>1.130840656075606</v>
       </c>
       <c r="I639">
         <v>35</v>
@@ -21448,10 +21472,10 @@
         <v>0.9291123786127875</v>
       </c>
       <c r="G640">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H640">
-        <v>0.6412419700794157</v>
+        <v>0.6552085699691385</v>
       </c>
       <c r="I640">
         <v>4</v>
@@ -21481,10 +21505,10 @@
         <v>1.911937498862678</v>
       </c>
       <c r="G641">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H641">
-        <v>1.319554659544971</v>
+        <v>1.348295279813793</v>
       </c>
       <c r="I641">
         <v>45</v>
@@ -21514,10 +21538,10 @@
         <v>2.023549657207091</v>
       </c>
       <c r="G642">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H642">
-        <v>1.396585599987767</v>
+        <v>1.427003996157877</v>
       </c>
       <c r="I642">
         <v>47</v>
@@ -21535,13 +21559,25 @@
       <c r="C643">
         <v>625</v>
       </c>
+      <c r="D643">
+        <v>30779.92565</v>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>other_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="F643">
+        <v>2.030544216080652</v>
+      </c>
       <c r="G643">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
+      </c>
+      <c r="H643">
+        <v>1.431936547938054</v>
+      </c>
+      <c r="I643">
+        <v>48</v>
       </c>
     </row>
     <row r="644">
@@ -21568,10 +21604,10 @@
         <v>1.722212539357844</v>
       </c>
       <c r="G644">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H644">
-        <v>1.188612903083</v>
+        <v>1.214501540470641</v>
       </c>
       <c r="I644">
         <v>41</v>
@@ -21601,10 +21637,10 @@
         <v>0.8086699302884396</v>
       </c>
       <c r="G645">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H645">
-        <v>0.5581166618578144</v>
+        <v>0.5702727471917024</v>
       </c>
       <c r="I645">
         <v>3</v>
@@ -21634,10 +21670,10 @@
         <v>0.9951797232199359</v>
       </c>
       <c r="G646">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H646">
-        <v>0.6868394189876488</v>
+        <v>0.7017991561868563</v>
       </c>
       <c r="I646">
         <v>8</v>
@@ -21667,10 +21703,10 @@
         <v>1.332223226835592</v>
       </c>
       <c r="G647">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H647">
-        <v>0.9194554568706659</v>
+        <v>0.9394816982611732</v>
       </c>
       <c r="I647">
         <v>25</v>
@@ -21700,10 +21736,10 @@
         <v>1.452483884490658</v>
       </c>
       <c r="G648">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H648">
-        <v>1.002455299314826</v>
+        <v>1.024289322548097</v>
       </c>
       <c r="I648">
         <v>31</v>
@@ -21733,13 +21769,13 @@
         <v>2.078509820622562</v>
       </c>
       <c r="G649">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H649">
-        <v>1.434517247736388</v>
+        <v>1.465761815885224</v>
       </c>
       <c r="I649">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="650">
@@ -21766,10 +21802,10 @@
         <v>1.176024938556992</v>
       </c>
       <c r="G650">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H650">
-        <v>0.8116526760613654</v>
+        <v>0.8293309140821361</v>
       </c>
       <c r="I650">
         <v>13</v>
@@ -21799,10 +21835,10 @@
         <v>1.266123223323891</v>
       </c>
       <c r="G651">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H651">
-        <v>0.8738354678900174</v>
+        <v>0.8928680810359678</v>
       </c>
       <c r="I651">
         <v>17</v>
@@ -22949,7 +22985,7 @@
         <v>9</v>
       </c>
       <c r="N2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2">
         <v>36</v>
@@ -23001,7 +23037,7 @@
         <v>36</v>
       </c>
       <c r="N3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O3">
         <v>45</v>
@@ -23020,7 +23056,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4">
         <v>32</v>
@@ -23053,13 +23089,13 @@
         <v>2</v>
       </c>
       <c r="N4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4">
         <v>43</v>
       </c>
       <c r="P4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -23105,7 +23141,7 @@
         <v>22</v>
       </c>
       <c r="N5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O5">
         <v>26</v>
@@ -23157,7 +23193,7 @@
         <v>24</v>
       </c>
       <c r="N6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6">
         <v>23</v>
@@ -23209,7 +23245,7 @@
         <v>18</v>
       </c>
       <c r="N7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O7">
         <v>41</v>
@@ -23228,7 +23264,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>19</v>
@@ -23329,7 +23365,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>38</v>
@@ -23362,7 +23398,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O10">
         <v>39</v>
@@ -23466,7 +23502,7 @@
         <v>30</v>
       </c>
       <c r="N12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O12">
         <v>38</v>
@@ -23518,7 +23554,7 @@
         <v>19</v>
       </c>
       <c r="N13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O13">
         <v>11</v>
@@ -23622,7 +23658,7 @@
         <v>20</v>
       </c>
       <c r="N15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15">
         <v>16</v>
@@ -23693,7 +23729,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17">
         <v>44</v>
@@ -23745,7 +23781,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18">
         <v>14</v>
@@ -23778,7 +23814,7 @@
         <v>33</v>
       </c>
       <c r="N18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O18">
         <v>24</v>
@@ -23830,7 +23866,7 @@
         <v>44</v>
       </c>
       <c r="N19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O19">
         <v>42</v>
@@ -23882,7 +23918,7 @@
         <v>47</v>
       </c>
       <c r="N20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O20">
         <v>3</v>
@@ -23953,7 +23989,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -24057,7 +24093,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>25</v>
@@ -24142,10 +24178,10 @@
         <v>26</v>
       </c>
       <c r="N25">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O25">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P25">
         <v>43</v>
@@ -24161,7 +24197,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -24194,7 +24230,7 @@
         <v>39</v>
       </c>
       <c r="N26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O26">
         <v>31</v>
@@ -24213,7 +24249,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D27">
         <v>18</v>
@@ -24246,10 +24282,10 @@
         <v>32</v>
       </c>
       <c r="N27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O27">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P27">
         <v>40</v>
@@ -24298,7 +24334,7 @@
         <v>37</v>
       </c>
       <c r="N28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O28">
         <v>20</v>
@@ -24350,7 +24386,7 @@
         <v>1</v>
       </c>
       <c r="N29">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O29">
         <v>40</v>
@@ -24369,7 +24405,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -24421,7 +24457,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D31">
         <v>45</v>
@@ -24454,7 +24490,7 @@
         <v>25</v>
       </c>
       <c r="N31">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O31">
         <v>17</v>
@@ -24506,10 +24542,10 @@
         <v>13</v>
       </c>
       <c r="N32">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O32">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P32">
         <v>20</v>
@@ -24577,7 +24613,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -24610,7 +24646,7 @@
         <v>31</v>
       </c>
       <c r="N34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O34">
         <v>22</v>
@@ -24785,7 +24821,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>28</v>
@@ -24818,7 +24854,7 @@
         <v>15</v>
       </c>
       <c r="N38">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O38">
         <v>34</v>
@@ -24941,7 +24977,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -24974,10 +25010,10 @@
         <v>27</v>
       </c>
       <c r="N41">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O41">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P41">
         <v>45</v>
@@ -24993,7 +25029,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42">
         <v>34</v>
@@ -25026,7 +25062,7 @@
         <v>48</v>
       </c>
       <c r="N42">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -25045,7 +25081,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D43">
         <v>12</v>
@@ -25077,6 +25113,15 @@
       <c r="M43">
         <v>11</v>
       </c>
+      <c r="N43">
+        <v>22</v>
+      </c>
+      <c r="O43">
+        <v>46</v>
+      </c>
+      <c r="P43">
+        <v>48</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -25088,7 +25133,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D44">
         <v>41</v>
@@ -25121,7 +25166,7 @@
         <v>3</v>
       </c>
       <c r="N44">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O44">
         <v>33</v>
@@ -25173,7 +25218,7 @@
         <v>8</v>
       </c>
       <c r="N45">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O45">
         <v>7</v>
@@ -25244,7 +25289,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -25277,7 +25322,7 @@
         <v>10</v>
       </c>
       <c r="N47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O47">
         <v>12</v>
@@ -25329,7 +25374,7 @@
         <v>23</v>
       </c>
       <c r="N48">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O48">
         <v>29</v>
@@ -25387,7 +25432,7 @@
         <v>44</v>
       </c>
       <c r="P49">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -25452,7 +25497,7 @@
         </is>
       </c>
       <c r="C51">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D51">
         <v>21</v>
